--- a/data/source/weekly/cs-en-us-026pct.xlsx
+++ b/data/source/weekly/cs-en-us-026pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
-        <v>1</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -902,13 +902,13 @@
         <v>21</v>
       </c>
       <c r="F15" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>3</v>
@@ -920,7 +920,7 @@
         <v>-25</v>
       </c>
       <c r="L15" s="14">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="M15" s="14">
         <v>50</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
         <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>-44.444444444444</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="I16" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J16" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K16" s="14">
-        <v>-57.142857142857</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="L16" s="14">
-        <v>-60</v>
+        <v>-56.25</v>
       </c>
       <c r="M16" s="14">
-        <v>-64.705882352941</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="N16" s="14">
-        <v>-91.176470588235</v>
+        <v>-91.764705882352</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,37 +978,37 @@
         <v>2</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>-60</v>
+        <v>100</v>
       </c>
       <c r="F17" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G17" s="15">
         <v>12</v>
       </c>
       <c r="H17" s="14">
-        <v>-8.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I17" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="J17" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K17" s="14">
-        <v>-11.764705882352</v>
+        <v>-5.555555555555</v>
       </c>
       <c r="L17" s="14">
-        <v>-21.052631578947</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="M17" s="14">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="N17" s="14">
-        <v>-42.307692307692</v>
+        <v>-45.161290322580</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1025,31 +1025,31 @@
         <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>-37.5</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="15">
         <v>7</v>
       </c>
       <c r="J18" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K18" s="14">
+        <v>-36.363636363636</v>
+      </c>
+      <c r="L18" s="14">
         <v>-22.222222222222</v>
-      </c>
-      <c r="L18" s="14">
-        <v>-12.5</v>
       </c>
       <c r="M18" s="14">
         <v>-22.222222222222</v>
       </c>
       <c r="N18" s="14">
-        <v>-90.789473684210</v>
+        <v>-91.860465116279</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,78 +1060,78 @@
         <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E19" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F19" s="15">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G19" s="15">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H19" s="14">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="I19" s="15">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="J19" s="15">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K19" s="14">
-        <v>-8</v>
+        <v>3.571428571428</v>
       </c>
       <c r="L19" s="14">
-        <v>-43.902439024390</v>
+        <v>-39.583333333333</v>
       </c>
       <c r="M19" s="14">
-        <v>0</v>
+        <v>11.538461538461</v>
       </c>
       <c r="N19" s="14">
-        <v>-68.055555555555</v>
+        <v>-65.476190476190</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
-      <c r="E20" s="14">
-        <v>-100</v>
+      <c r="C20" s="15">
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G20" s="15">
         <v>1</v>
       </c>
       <c r="H20" s="14">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="I20" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J20" s="15">
         <v>1</v>
       </c>
       <c r="K20" s="14">
+        <v>300</v>
+      </c>
+      <c r="L20" s="14">
+        <v>33.333333333333</v>
+      </c>
+      <c r="M20" s="14">
         <v>100</v>
       </c>
-      <c r="L20" s="14">
-        <v>0</v>
-      </c>
-      <c r="M20" s="14">
-        <v>0</v>
-      </c>
       <c r="N20" s="14">
-        <v>-96.491228070175</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="E21" s="18">
-        <v>-40</v>
+        <v>57.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="G21" s="17">
         <v>48</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.416666666666</v>
+        <v>-18.75</v>
       </c>
       <c r="I21" s="17">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="J21" s="17">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="K21" s="18">
-        <v>-20</v>
+        <v>-12.987012987013</v>
       </c>
       <c r="L21" s="18">
-        <v>-34.883720930232</v>
+        <v>-33</v>
       </c>
       <c r="M21" s="18">
-        <v>-12.5</v>
+        <v>-1.470588235294</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.699346405228</v>
+        <v>-81.440443213296</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,29 +1182,29 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
+      <c r="D22" s="15">
         <v>1</v>
       </c>
+      <c r="E22" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I22" s="15">
         <v>1</v>
       </c>
       <c r="J22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K22" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L22" s="14">
         <v>0</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D23" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F23" s="15">
         <v>10</v>
       </c>
       <c r="G23" s="15">
+        <v>15</v>
+      </c>
+      <c r="H23" s="14">
+        <v>-33.333333333333</v>
+      </c>
+      <c r="I23" s="15">
         <v>13</v>
       </c>
-      <c r="H23" s="14">
-        <v>-23.076923076923</v>
-      </c>
-      <c r="I23" s="15">
-        <v>12</v>
-      </c>
       <c r="J23" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K23" s="14">
-        <v>-25</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="L23" s="14">
-        <v>-33.333333333333</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="M23" s="14">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D24" s="15">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E24" s="14">
-        <v>-58.333333333333</v>
+        <v>-55.555555555555</v>
       </c>
       <c r="F24" s="15">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G24" s="15">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="H24" s="14">
-        <v>-28.947368421052</v>
+        <v>-53.488372093023</v>
       </c>
       <c r="I24" s="15">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="J24" s="15">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K24" s="14">
-        <v>-23.404255319148</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L24" s="14">
-        <v>2.857142857142</v>
+        <v>-2.439024390243</v>
       </c>
       <c r="M24" s="14">
-        <v>-29.411764705882</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
-      </c>
-      <c r="D25" s="15">
-        <v>3</v>
-      </c>
-      <c r="E25" s="14">
-        <v>-66.666666666666</v>
+        <v>2</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H25" s="14">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J25" s="15">
         <v>10</v>
       </c>
       <c r="K25" s="14">
-        <v>-50</v>
+        <v>-30</v>
       </c>
       <c r="L25" s="14">
-        <v>-37.5</v>
+        <v>-30</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D26" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E26" s="14">
+        <v>40</v>
+      </c>
+      <c r="F26" s="15">
+        <v>20</v>
+      </c>
+      <c r="G26" s="15">
+        <v>18</v>
+      </c>
+      <c r="H26" s="14">
+        <v>11.111111111111</v>
+      </c>
+      <c r="I26" s="15">
+        <v>27</v>
+      </c>
+      <c r="J26" s="15">
+        <v>33</v>
+      </c>
+      <c r="K26" s="14">
+        <v>-18.181818181818</v>
+      </c>
+      <c r="L26" s="14">
+        <v>-32.5</v>
+      </c>
+      <c r="M26" s="14">
         <v>0</v>
-      </c>
-      <c r="F26" s="15">
-        <v>17</v>
-      </c>
-      <c r="G26" s="15">
-        <v>16</v>
-      </c>
-      <c r="H26" s="14">
-        <v>6.25</v>
-      </c>
-      <c r="I26" s="15">
-        <v>20</v>
-      </c>
-      <c r="J26" s="15">
-        <v>28</v>
-      </c>
-      <c r="K26" s="14">
-        <v>-28.571428571428</v>
-      </c>
-      <c r="L26" s="14">
-        <v>-45.945945945945</v>
-      </c>
-      <c r="M26" s="14">
-        <v>-16.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,13 +1394,13 @@
         <v>21</v>
       </c>
       <c r="F27" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>2</v>
       </c>
       <c r="H27" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>3</v>
@@ -1412,7 +1412,7 @@
         <v>-40</v>
       </c>
       <c r="L27" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
-        <v>1</v>
+      <c r="C28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D28" s="15">
         <v>1</v>
       </c>
       <c r="E28" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28" s="15">
         <v>3</v>
       </c>
       <c r="H28" s="14">
-        <v>33.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="15">
         <v>9</v>
       </c>
       <c r="J28" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K28" s="14">
-        <v>200</v>
+        <v>125</v>
       </c>
       <c r="L28" s="14">
         <v>350</v>
@@ -1557,23 +1557,23 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="G31" s="15">
+      <c r="F31" s="15">
         <v>1</v>
       </c>
-      <c r="H31" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="J31" s="15">
+      <c r="G31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="I31" s="15">
         <v>1</v>
       </c>
-      <c r="K31" s="14">
-        <v>-100</v>
+      <c r="J31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-026pct.xlsx
+++ b/data/source/weekly/cs-en-us-026pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H16" s="14">
-        <v>-55.555555555555</v>
+        <v>-37.5</v>
       </c>
       <c r="I16" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="J16" s="15">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K16" s="14">
-        <v>-53.333333333333</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="L16" s="14">
-        <v>-56.25</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="M16" s="14">
-        <v>-61.111111111111</v>
+        <v>-50</v>
       </c>
       <c r="N16" s="14">
-        <v>-91.764705882352</v>
+        <v>-90.291262135922</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
         <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="F17" s="15">
+        <v>10</v>
+      </c>
+      <c r="G17" s="15">
         <v>9</v>
       </c>
-      <c r="G17" s="15">
-        <v>12</v>
-      </c>
       <c r="H17" s="14">
-        <v>-25</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I17" s="15">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J17" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K17" s="14">
-        <v>-5.555555555555</v>
+        <v>5.263157894736</v>
       </c>
       <c r="L17" s="14">
-        <v>-22.727272727272</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="M17" s="14">
-        <v>70</v>
+        <v>53.846153846153</v>
       </c>
       <c r="N17" s="14">
-        <v>-45.161290322580</v>
+        <v>-48.717948717948</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
         <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G18" s="15">
         <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>-42.857142857142</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I18" s="15">
         <v>7</v>
       </c>
       <c r="J18" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K18" s="14">
+        <v>-41.666666666666</v>
+      </c>
+      <c r="L18" s="14">
         <v>-36.363636363636</v>
       </c>
-      <c r="L18" s="14">
-        <v>-22.222222222222</v>
-      </c>
       <c r="M18" s="14">
-        <v>-22.222222222222</v>
+        <v>-30</v>
       </c>
       <c r="N18" s="14">
-        <v>-91.860465116279</v>
+        <v>-92.708333333333</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,63 +1057,63 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="15">
         <v>3</v>
       </c>
       <c r="E19" s="14">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F19" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G19" s="15">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H19" s="14">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="I19" s="15">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="J19" s="15">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K19" s="14">
-        <v>3.571428571428</v>
+        <v>9.677419354838</v>
       </c>
       <c r="L19" s="14">
-        <v>-39.583333333333</v>
+        <v>-38.181818181818</v>
       </c>
       <c r="M19" s="14">
-        <v>11.538461538461</v>
+        <v>6.25</v>
       </c>
       <c r="N19" s="14">
-        <v>-65.476190476190</v>
+        <v>-64.583333333333</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="15">
         <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F20" s="15">
-        <v>3</v>
       </c>
       <c r="G20" s="15">
         <v>1</v>
       </c>
       <c r="H20" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I20" s="15">
         <v>4</v>
@@ -1125,13 +1125,13 @@
         <v>300</v>
       </c>
       <c r="L20" s="14">
-        <v>33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M20" s="14">
         <v>100</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.117647058823</v>
+        <v>-94.666666666666</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1148,66 +1148,66 @@
         <v>57.142857142857</v>
       </c>
       <c r="F21" s="17">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G21" s="17">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.75</v>
+        <v>-11.627906976744</v>
       </c>
       <c r="I21" s="17">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="J21" s="17">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="K21" s="18">
-        <v>-12.987012987013</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L21" s="18">
-        <v>-33</v>
+        <v>-30.973451327433</v>
       </c>
       <c r="M21" s="18">
-        <v>-1.470588235294</v>
+        <v>-2.5</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.440443213296</v>
+        <v>-81.25</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="15">
+        <v>1</v>
       </c>
       <c r="D22" s="15">
         <v>1</v>
       </c>
       <c r="E22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F22" s="15">
+        <v>1</v>
       </c>
       <c r="G22" s="15">
+        <v>3</v>
+      </c>
+      <c r="H22" s="14">
+        <v>-66.666666666666</v>
+      </c>
+      <c r="I22" s="15">
         <v>2</v>
       </c>
-      <c r="H22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="I22" s="15">
-        <v>1</v>
-      </c>
       <c r="J22" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K22" s="14">
-        <v>-75</v>
+        <v>-60</v>
       </c>
       <c r="L22" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22" s="14">
         <v>0</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="15">
         <v>1</v>
       </c>
-      <c r="D23" s="15">
-        <v>2</v>
-      </c>
-      <c r="E23" s="14">
-        <v>-50</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="15">
+        <v>8</v>
+      </c>
+      <c r="G23" s="15">
         <v>10</v>
       </c>
-      <c r="G23" s="15">
-        <v>15</v>
-      </c>
       <c r="H23" s="14">
-        <v>-33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I23" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J23" s="15">
         <v>18</v>
       </c>
       <c r="K23" s="14">
-        <v>-27.777777777777</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L23" s="14">
-        <v>-40.909090909090</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="M23" s="14">
-        <v>30</v>
+        <v>27.272727272727</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D24" s="15">
         <v>9</v>
       </c>
       <c r="E24" s="14">
-        <v>-55.555555555555</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="F24" s="15">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G24" s="15">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H24" s="14">
-        <v>-53.488372093023</v>
+        <v>-56.410256410256</v>
       </c>
       <c r="I24" s="15">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="J24" s="15">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="K24" s="14">
-        <v>-28.571428571428</v>
+        <v>-35.384615384615</v>
       </c>
       <c r="L24" s="14">
-        <v>-2.439024390243</v>
+        <v>-16</v>
       </c>
       <c r="M24" s="14">
-        <v>-27.272727272727</v>
+        <v>-31.147540983606</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,7 +1303,7 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="13" t="s">
         <v>20</v>
@@ -1315,22 +1315,22 @@
         <v>4</v>
       </c>
       <c r="G25" s="15">
+        <v>4</v>
+      </c>
+      <c r="H25" s="14">
+        <v>0</v>
+      </c>
+      <c r="I25" s="15">
         <v>8</v>
-      </c>
-      <c r="H25" s="14">
-        <v>-50</v>
-      </c>
-      <c r="I25" s="15">
-        <v>7</v>
       </c>
       <c r="J25" s="15">
         <v>10</v>
       </c>
       <c r="K25" s="14">
-        <v>-30</v>
+        <v>-20</v>
       </c>
       <c r="L25" s="14">
-        <v>-30</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="D26" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>40</v>
+        <v>-50</v>
       </c>
       <c r="F26" s="15">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G26" s="15">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="H26" s="14">
-        <v>11.111111111111</v>
+        <v>45.454545454545</v>
       </c>
       <c r="I26" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J26" s="15">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K26" s="14">
-        <v>-18.181818181818</v>
+        <v>-20</v>
       </c>
       <c r="L26" s="14">
-        <v>-32.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M26" s="14">
-        <v>0</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1412,7 +1412,7 @@
         <v>-40</v>
       </c>
       <c r="L27" s="14">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,11 +1428,11 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
         <v>2</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="15">
-        <v>1</v>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="15">
-        <v>1</v>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-026pct.xlsx
+++ b/data/source/weekly/cs-en-us-026pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -892,41 +892,41 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="15">
+        <v>1</v>
+      </c>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>0</v>
       </c>
       <c r="F15" s="15">
         <v>2</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="14">
+        <v>100</v>
+      </c>
+      <c r="I15" s="15">
+        <v>5</v>
+      </c>
+      <c r="J15" s="15">
+        <v>5</v>
+      </c>
+      <c r="K15" s="14">
         <v>0</v>
       </c>
-      <c r="I15" s="15">
-        <v>3</v>
-      </c>
-      <c r="J15" s="15">
-        <v>4</v>
-      </c>
-      <c r="K15" s="14">
-        <v>-25</v>
-      </c>
       <c r="L15" s="14">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="M15" s="14">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N15" s="14">
-        <v>-25</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,13 +934,13 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
         <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>50</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
         <v>5</v>
@@ -952,22 +952,22 @@
         <v>-37.5</v>
       </c>
       <c r="I16" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J16" s="15">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K16" s="14">
-        <v>-41.176470588235</v>
+        <v>-42.105263157894</v>
       </c>
       <c r="L16" s="14">
-        <v>-41.176470588235</v>
+        <v>-45</v>
       </c>
       <c r="M16" s="14">
-        <v>-50</v>
+        <v>-47.619047619047</v>
       </c>
       <c r="N16" s="14">
-        <v>-90.291262135922</v>
+        <v>-91.338582677165</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>3</v>
-      </c>
-      <c r="D17" s="15">
-        <v>1</v>
-      </c>
-      <c r="E17" s="14">
-        <v>200</v>
+        <v>4</v>
+      </c>
+      <c r="D17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F17" s="15">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G17" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H17" s="14">
-        <v>11.111111111111</v>
+        <v>57.142857142857</v>
       </c>
       <c r="I17" s="15">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J17" s="15">
         <v>19</v>
       </c>
       <c r="K17" s="14">
-        <v>5.263157894736</v>
+        <v>26.315789473684</v>
       </c>
       <c r="L17" s="14">
-        <v>-16.666666666666</v>
+        <v>-4</v>
       </c>
       <c r="M17" s="14">
-        <v>53.846153846153</v>
+        <v>71.428571428571</v>
       </c>
       <c r="N17" s="14">
-        <v>-48.717948717948</v>
+        <v>-42.857142857142</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>2</v>
       </c>
       <c r="D18" s="15">
         <v>1</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F18" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H18" s="14">
-        <v>-85.714285714285</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I18" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J18" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K18" s="14">
-        <v>-41.666666666666</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="L18" s="14">
-        <v>-36.363636363636</v>
+        <v>-25</v>
       </c>
       <c r="M18" s="14">
-        <v>-30</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="N18" s="14">
-        <v>-92.708333333333</v>
+        <v>-91.428571428571</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>7</v>
+      </c>
+      <c r="D19" s="15">
         <v>5</v>
       </c>
-      <c r="D19" s="15">
-        <v>3</v>
-      </c>
       <c r="E19" s="14">
-        <v>66.666666666666</v>
+        <v>40</v>
       </c>
       <c r="F19" s="15">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="G19" s="15">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H19" s="14">
-        <v>12.5</v>
+        <v>60</v>
       </c>
       <c r="I19" s="15">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="J19" s="15">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="K19" s="14">
-        <v>9.677419354838</v>
+        <v>13.888888888888</v>
       </c>
       <c r="L19" s="14">
-        <v>-38.181818181818</v>
+        <v>-32.786885245901</v>
       </c>
       <c r="M19" s="14">
-        <v>6.25</v>
+        <v>7.894736842105</v>
       </c>
       <c r="N19" s="14">
-        <v>-64.583333333333</v>
+        <v>-62.037037037037</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1125,13 +1125,13 @@
         <v>300</v>
       </c>
       <c r="L20" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="M20" s="14">
         <v>100</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.666666666666</v>
+        <v>-95.061728395061</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E21" s="18">
-        <v>57.142857142857</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F21" s="17">
+        <v>46</v>
+      </c>
+      <c r="G21" s="17">
         <v>38</v>
       </c>
-      <c r="G21" s="17">
-        <v>43</v>
-      </c>
       <c r="H21" s="18">
-        <v>-11.627906976744</v>
+        <v>21.052631578947</v>
       </c>
       <c r="I21" s="17">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="J21" s="17">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="K21" s="18">
-        <v>-7.142857142857</v>
+        <v>1.075268817204</v>
       </c>
       <c r="L21" s="18">
-        <v>-30.973451327433</v>
+        <v>-24.8</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.5</v>
+        <v>4.444444444444</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.25</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="15">
         <v>1</v>
       </c>
-      <c r="D22" s="15">
-        <v>1</v>
-      </c>
-      <c r="E22" s="14">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
+        <v>2</v>
+      </c>
+      <c r="G22" s="15">
+        <v>2</v>
+      </c>
+      <c r="H22" s="14">
         <v>0</v>
       </c>
-      <c r="F22" s="15">
-        <v>1</v>
-      </c>
-      <c r="G22" s="15">
+      <c r="I22" s="15">
         <v>3</v>
-      </c>
-      <c r="H22" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="I22" s="15">
-        <v>2</v>
       </c>
       <c r="J22" s="15">
         <v>5</v>
       </c>
       <c r="K22" s="14">
-        <v>-60</v>
+        <v>-40</v>
       </c>
       <c r="L22" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M22" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>1</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D23" s="15">
+        <v>2</v>
+      </c>
+      <c r="E23" s="14">
+        <v>50</v>
       </c>
       <c r="F23" s="15">
+        <v>9</v>
+      </c>
+      <c r="G23" s="15">
         <v>8</v>
       </c>
-      <c r="G23" s="15">
-        <v>10</v>
-      </c>
       <c r="H23" s="14">
-        <v>-20</v>
+        <v>12.5</v>
       </c>
       <c r="I23" s="15">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="J23" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K23" s="14">
-        <v>-22.222222222222</v>
+        <v>-10</v>
       </c>
       <c r="L23" s="14">
-        <v>-41.666666666666</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M23" s="14">
-        <v>27.272727272727</v>
+        <v>38.461538461538</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D24" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E24" s="14">
-        <v>-77.777777777777</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="F24" s="15">
         <v>17</v>
       </c>
       <c r="G24" s="15">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="H24" s="14">
-        <v>-56.410256410256</v>
+        <v>-60.465116279069</v>
       </c>
       <c r="I24" s="15">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="J24" s="15">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="K24" s="14">
-        <v>-35.384615384615</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="L24" s="14">
-        <v>-16</v>
+        <v>-20</v>
       </c>
       <c r="M24" s="14">
-        <v>-31.147540983606</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,32 +1302,32 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
-        <v>1</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="15">
+        <v>2</v>
+      </c>
+      <c r="E25" s="14">
+        <v>-100</v>
       </c>
       <c r="F25" s="15">
         <v>4</v>
       </c>
       <c r="G25" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H25" s="14">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="I25" s="15">
         <v>8</v>
       </c>
       <c r="J25" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K25" s="14">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L25" s="14">
         <v>-33.333333333333</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D26" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
         <v>-50</v>
       </c>
       <c r="F26" s="15">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G26" s="15">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H26" s="14">
-        <v>45.454545454545</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="I26" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J26" s="15">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="K26" s="14">
-        <v>-20</v>
+        <v>-23.076923076923</v>
       </c>
       <c r="L26" s="14">
-        <v>-33.333333333333</v>
+        <v>-34.782608695652</v>
       </c>
       <c r="M26" s="14">
-        <v>-3.448275862068</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="15">
+        <v>1</v>
+      </c>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>0</v>
       </c>
       <c r="F27" s="15">
         <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I27" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J27" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K27" s="14">
-        <v>-40</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L27" s="14">
-        <v>-25</v>
+        <v>25</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="15">
+        <v>3</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
+        <v>4</v>
+      </c>
+      <c r="G28" s="15">
         <v>2</v>
       </c>
-      <c r="G28" s="15">
-        <v>3</v>
-      </c>
       <c r="H28" s="14">
-        <v>-33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="I28" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J28" s="15">
         <v>4</v>
       </c>
       <c r="K28" s="14">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="L28" s="14">
-        <v>350</v>
+        <v>450</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1558,7 +1558,7 @@
         <v>21</v>
       </c>
       <c r="F31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="13" t="s">
         <v>20</v>
@@ -1567,7 +1567,7 @@
         <v>21</v>
       </c>
       <c r="I31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-026pct.xlsx
+++ b/data/source/weekly/cs-en-us-026pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="15">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="15">
         <v>1</v>
-      </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>0</v>
-      </c>
-      <c r="F15" s="15">
-        <v>2</v>
       </c>
       <c r="G15" s="15">
         <v>1</v>
       </c>
       <c r="H15" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I15" s="15">
         <v>5</v>
@@ -933,82 +933,82 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
         <v>5</v>
       </c>
       <c r="G16" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>-37.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I16" s="15">
         <v>11</v>
       </c>
       <c r="J16" s="15">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="K16" s="14">
-        <v>-42.105263157894</v>
+        <v>-52.173913043478</v>
       </c>
       <c r="L16" s="14">
-        <v>-45</v>
+        <v>-56</v>
       </c>
       <c r="M16" s="14">
-        <v>-47.619047619047</v>
+        <v>-57.692307692307</v>
       </c>
       <c r="N16" s="14">
-        <v>-91.338582677165</v>
+        <v>-92.465753424657</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>4</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>21</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="15">
+        <v>3</v>
+      </c>
+      <c r="E17" s="14">
+        <v>-100</v>
       </c>
       <c r="F17" s="15">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G17" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H17" s="14">
-        <v>57.142857142857</v>
+        <v>80</v>
       </c>
       <c r="I17" s="15">
         <v>24</v>
       </c>
       <c r="J17" s="15">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="K17" s="14">
-        <v>26.315789473684</v>
+        <v>9.090909090909</v>
       </c>
       <c r="L17" s="14">
-        <v>-4</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="M17" s="14">
-        <v>71.428571428571</v>
+        <v>60</v>
       </c>
       <c r="N17" s="14">
-        <v>-42.857142857142</v>
+        <v>-46.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
-        <v>100</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H18" s="14">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I18" s="15">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J18" s="15">
         <v>13</v>
       </c>
       <c r="K18" s="14">
-        <v>-30.769230769230</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="L18" s="14">
-        <v>-25</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="M18" s="14">
-        <v>-18.181818181818</v>
+        <v>-8.333333333333</v>
       </c>
       <c r="N18" s="14">
-        <v>-91.428571428571</v>
+        <v>-90.677966101694</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
+        <v>5</v>
+      </c>
+      <c r="D19" s="15">
         <v>7</v>
       </c>
-      <c r="D19" s="15">
-        <v>5</v>
-      </c>
       <c r="E19" s="14">
-        <v>40</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F19" s="15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" s="15">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H19" s="14">
-        <v>60</v>
+        <v>27.777777777777</v>
       </c>
       <c r="I19" s="15">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="J19" s="15">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="K19" s="14">
-        <v>13.888888888888</v>
+        <v>6.976744186046</v>
       </c>
       <c r="L19" s="14">
-        <v>-32.786885245901</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M19" s="14">
-        <v>7.894736842105</v>
+        <v>0</v>
       </c>
       <c r="N19" s="14">
-        <v>-62.037037037037</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1100,38 +1100,38 @@
       <c r="C20" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="D20" s="15">
+        <v>3</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
         <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H20" s="14">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="15">
         <v>4</v>
       </c>
       <c r="J20" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K20" s="14">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="L20" s="14">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="M20" s="14">
         <v>100</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.061728395061</v>
+        <v>-95.555555555555</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D21" s="17">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>66.666666666666</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="F21" s="17">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="G21" s="17">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H21" s="18">
-        <v>21.052631578947</v>
+        <v>10</v>
       </c>
       <c r="I21" s="17">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="J21" s="17">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="K21" s="18">
-        <v>1.075268817204</v>
+        <v>-8.181818181818</v>
       </c>
       <c r="L21" s="18">
-        <v>-24.8</v>
+        <v>-28.368794326241</v>
       </c>
       <c r="M21" s="18">
-        <v>4.444444444444</v>
+        <v>-3.809523809523</v>
       </c>
       <c r="N21" s="18">
-        <v>-80</v>
+        <v>-80.651340996168</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="15">
         <v>2</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J22" s="15">
         <v>5</v>
       </c>
       <c r="K22" s="14">
-        <v>-40</v>
+        <v>-20</v>
       </c>
       <c r="L22" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M22" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
+        <v>1</v>
+      </c>
+      <c r="D23" s="15">
         <v>3</v>
       </c>
-      <c r="D23" s="15">
-        <v>2</v>
-      </c>
       <c r="E23" s="14">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G23" s="15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H23" s="14">
-        <v>12.5</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I23" s="15">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" s="15">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="K23" s="14">
-        <v>-10</v>
+        <v>-17.391304347826</v>
       </c>
       <c r="L23" s="14">
-        <v>-35.714285714285</v>
+        <v>-38.709677419354</v>
       </c>
       <c r="M23" s="14">
-        <v>38.461538461538</v>
+        <v>18.75</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="D24" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E24" s="14">
-        <v>-61.538461538461</v>
+        <v>-20</v>
       </c>
       <c r="F24" s="15">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G24" s="15">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H24" s="14">
-        <v>-60.465116279069</v>
+        <v>-50</v>
       </c>
       <c r="I24" s="15">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="J24" s="15">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="K24" s="14">
-        <v>-38.461538461538</v>
+        <v>-36.559139784946</v>
       </c>
       <c r="L24" s="14">
-        <v>-20</v>
+        <v>-16.901408450704</v>
       </c>
       <c r="M24" s="14">
-        <v>-27.272727272727</v>
+        <v>-22.368421052631</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="15">
+        <v>1</v>
       </c>
       <c r="D25" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F25" s="15">
         <v>4</v>
       </c>
       <c r="G25" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H25" s="14">
-        <v>-20</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I25" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J25" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K25" s="14">
-        <v>-33.333333333333</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="L25" s="14">
-        <v>-33.333333333333</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="E26" s="14">
-        <v>-50</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="F26" s="15">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G26" s="15">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="H26" s="14">
-        <v>-7.142857142857</v>
+        <v>-37.5</v>
       </c>
       <c r="I26" s="15">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="J26" s="15">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="K26" s="14">
-        <v>-23.076923076923</v>
+        <v>-32.692307692307</v>
       </c>
       <c r="L26" s="14">
-        <v>-34.782608695652</v>
+        <v>-30</v>
       </c>
       <c r="M26" s="14">
-        <v>-21.052631578947</v>
+        <v>-18.604651162790</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="15">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="15">
         <v>1</v>
-      </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>0</v>
-      </c>
-      <c r="F27" s="15">
-        <v>2</v>
       </c>
       <c r="G27" s="15">
         <v>1</v>
       </c>
       <c r="H27" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I27" s="15">
         <v>5</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F28" s="15">
         <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="15">
-        <v>4</v>
       </c>
       <c r="G28" s="15">
         <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I28" s="15">
         <v>11</v>
       </c>
       <c r="J28" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K28" s="14">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="L28" s="14">
-        <v>450</v>
+        <v>266.666666666667</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>21</v>
       </c>
       <c r="N29" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,15 +1541,15 @@
         <v>21</v>
       </c>
       <c r="N30" s="14">
-        <v>-75</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
-        <v>1</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1575,8 +1575,8 @@
       <c r="K31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="13" t="s">
-        <v>21</v>
+      <c r="L31" s="14">
+        <v>50</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-026pct.xlsx
+++ b/data/source/weekly/cs-en-us-026pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,120 +895,120 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
       </c>
       <c r="F15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G15" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H15" s="14">
         <v>0</v>
       </c>
       <c r="I15" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J15" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K15" s="14">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="L15" s="14">
-        <v>150</v>
+        <v>250</v>
       </c>
       <c r="M15" s="14">
-        <v>66.666666666666</v>
+        <v>133.333333333333</v>
       </c>
       <c r="N15" s="14">
-        <v>25</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="15">
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
         <v>5</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J16" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K16" s="14">
-        <v>-52.173913043478</v>
+        <v>-52</v>
       </c>
       <c r="L16" s="14">
-        <v>-56</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M16" s="14">
-        <v>-57.692307692307</v>
+        <v>-61.290322580645</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.465753424657</v>
+        <v>-92.638036809816</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="15">
+        <v>4</v>
       </c>
       <c r="D17" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>-100</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="15">
+        <v>11</v>
+      </c>
+      <c r="G17" s="15">
         <v>9</v>
       </c>
-      <c r="G17" s="15">
-        <v>5</v>
-      </c>
       <c r="H17" s="14">
-        <v>80</v>
+        <v>22.222222222222</v>
       </c>
       <c r="I17" s="15">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J17" s="15">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K17" s="14">
-        <v>9.090909090909</v>
+        <v>3.703703703703</v>
       </c>
       <c r="L17" s="14">
-        <v>-11.111111111111</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M17" s="14">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="N17" s="14">
-        <v>-46.666666666666</v>
+        <v>-44</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="D18" s="15">
+        <v>1</v>
+      </c>
+      <c r="E18" s="14">
+        <v>100</v>
       </c>
       <c r="F18" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18" s="14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I18" s="15">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="J18" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K18" s="14">
-        <v>-15.384615384615</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="L18" s="14">
-        <v>-8.333333333333</v>
+        <v>8.333333333333</v>
       </c>
       <c r="M18" s="14">
-        <v>-8.333333333333</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="N18" s="14">
-        <v>-90.677966101694</v>
+        <v>-89.763779527559</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D19" s="15">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>-28.571428571428</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F19" s="15">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="G19" s="15">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="H19" s="14">
-        <v>27.777777777777</v>
+        <v>3.846153846153</v>
       </c>
       <c r="I19" s="15">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="J19" s="15">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="K19" s="14">
-        <v>6.976744186046</v>
+        <v>3.703703703703</v>
       </c>
       <c r="L19" s="14">
-        <v>-33.333333333333</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="M19" s="14">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N19" s="14">
-        <v>-60</v>
+        <v>-57.894736842105</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>2</v>
       </c>
       <c r="D20" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E20" s="14">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F20" s="15">
         <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="14">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="I20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J20" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K20" s="14">
+        <v>20</v>
+      </c>
+      <c r="L20" s="14">
         <v>0</v>
       </c>
-      <c r="L20" s="14">
-        <v>-33.333333333333</v>
-      </c>
       <c r="M20" s="14">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="N20" s="14">
-        <v>-95.555555555555</v>
+        <v>-93.684210526315</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>-58.823529411764</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="F21" s="17">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="G21" s="17">
-        <v>40</v>
+        <v>54</v>
       </c>
       <c r="H21" s="18">
-        <v>10</v>
+        <v>-1.851851851851</v>
       </c>
       <c r="I21" s="17">
-        <v>101</v>
+        <v>122</v>
       </c>
       <c r="J21" s="17">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.181818181818</v>
+        <v>-6.870229007633</v>
       </c>
       <c r="L21" s="18">
-        <v>-28.368794326241</v>
+        <v>-20.779220779220</v>
       </c>
       <c r="M21" s="18">
-        <v>-3.809523809523</v>
+        <v>1.666666666666</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.651340996168</v>
+        <v>-78.819444444444</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="15">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1192,10 +1192,10 @@
         <v>3</v>
       </c>
       <c r="G22" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="I22" s="15">
         <v>4</v>
@@ -1207,7 +1207,7 @@
         <v>-20</v>
       </c>
       <c r="L22" s="14">
-        <v>100</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M22" s="14">
         <v>100</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="14">
-        <v>-66.666666666666</v>
+        <v>50</v>
       </c>
       <c r="F23" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G23" s="15">
         <v>7</v>
       </c>
       <c r="H23" s="14">
-        <v>-14.285714285714</v>
+        <v>28.571428571428</v>
       </c>
       <c r="I23" s="15">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J23" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K23" s="14">
-        <v>-17.391304347826</v>
+        <v>-4</v>
       </c>
       <c r="L23" s="14">
-        <v>-38.709677419354</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M23" s="14">
-        <v>18.75</v>
+        <v>26.315789473684</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="D24" s="15">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="E24" s="14">
-        <v>-20</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F24" s="15">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G24" s="15">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="H24" s="14">
-        <v>-50</v>
+        <v>-41.860465116279</v>
       </c>
       <c r="I24" s="15">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="J24" s="15">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="K24" s="14">
-        <v>-36.559139784946</v>
+        <v>-32.323232323232</v>
       </c>
       <c r="L24" s="14">
-        <v>-16.901408450704</v>
+        <v>-14.102564102564</v>
       </c>
       <c r="M24" s="14">
-        <v>-22.368421052631</v>
+        <v>-19.277108433734</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1312,25 +1312,25 @@
         <v>0</v>
       </c>
       <c r="F25" s="15">
+        <v>3</v>
+      </c>
+      <c r="G25" s="15">
         <v>4</v>
       </c>
-      <c r="G25" s="15">
-        <v>3</v>
-      </c>
       <c r="H25" s="14">
-        <v>33.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I25" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J25" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K25" s="14">
-        <v>-30.769230769230</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L25" s="14">
-        <v>-35.714285714285</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E26" s="14">
-        <v>-61.538461538461</v>
+        <v>300</v>
       </c>
       <c r="F26" s="15">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G26" s="15">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="H26" s="14">
-        <v>-37.5</v>
+        <v>-23.809523809523</v>
       </c>
       <c r="I26" s="15">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="J26" s="15">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K26" s="14">
-        <v>-32.692307692307</v>
+        <v>-20.370370370370</v>
       </c>
       <c r="L26" s="14">
-        <v>-30</v>
+        <v>-27.118644067796</v>
       </c>
       <c r="M26" s="14">
-        <v>-18.604651162790</v>
+        <v>-6.521739130434</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="15">
+        <v>1</v>
+      </c>
+      <c r="E27" s="14">
+        <v>-100</v>
       </c>
       <c r="F27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
         <v>0</v>
       </c>
       <c r="I27" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J27" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K27" s="14">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="L27" s="14">
-        <v>25</v>
+        <v>75</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
+      <c r="C28" s="15">
+        <v>3</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="15">
+        <v>5</v>
+      </c>
+      <c r="G28" s="15">
         <v>1</v>
       </c>
-      <c r="E28" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="15">
-        <v>3</v>
-      </c>
-      <c r="G28" s="15">
-        <v>2</v>
-      </c>
       <c r="H28" s="14">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="I28" s="15">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J28" s="15">
         <v>5</v>
       </c>
       <c r="K28" s="14">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="L28" s="14">
-        <v>266.666666666667</v>
+        <v>300</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1496,8 +1496,8 @@
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="13" t="s">
-        <v>21</v>
+      <c r="M29" s="14">
+        <v>-50</v>
       </c>
       <c r="N29" s="14">
         <v>-80</v>
@@ -1537,8 +1537,8 @@
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="13" t="s">
-        <v>21</v>
+      <c r="M30" s="14">
+        <v>-50</v>
       </c>
       <c r="N30" s="14">
         <v>-80</v>

--- a/data/source/weekly/cs-en-us-026pct.xlsx
+++ b/data/source/weekly/cs-en-us-026pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -695,7 +695,7 @@
     <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="15">
         <v>2</v>
@@ -926,7 +926,7 @@
         <v>133.333333333333</v>
       </c>
       <c r="N15" s="14">
-        <v>75</v>
+        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D16" s="15">
         <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
         <v>10</v>
       </c>
       <c r="H16" s="14">
-        <v>-50</v>
+        <v>-60</v>
       </c>
       <c r="I16" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J16" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K16" s="14">
-        <v>-52</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="L16" s="14">
-        <v>-57.142857142857</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="M16" s="14">
-        <v>-61.290322580645</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.638036809816</v>
+        <v>-92.178770949720</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,72 +975,72 @@
         <v>24</v>
       </c>
       <c r="C17" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" s="14">
-        <v>-20</v>
+        <v>50</v>
       </c>
       <c r="F17" s="15">
         <v>11</v>
       </c>
       <c r="G17" s="15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H17" s="14">
-        <v>22.222222222222</v>
+        <v>10</v>
       </c>
       <c r="I17" s="15">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J17" s="15">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="K17" s="14">
-        <v>3.703703703703</v>
+        <v>6.896551724137</v>
       </c>
       <c r="L17" s="14">
-        <v>-6.666666666666</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="M17" s="14">
-        <v>33.333333333333</v>
+        <v>34.782608695652</v>
       </c>
       <c r="N17" s="14">
-        <v>-44</v>
+        <v>-47.457627118644</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="15">
         <v>2</v>
       </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
       <c r="E18" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
         <v>6</v>
       </c>
       <c r="G18" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H18" s="14">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="I18" s="15">
         <v>13</v>
       </c>
       <c r="J18" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K18" s="14">
-        <v>-7.142857142857</v>
+        <v>-18.75</v>
       </c>
       <c r="L18" s="14">
         <v>8.333333333333</v>
@@ -1049,7 +1049,7 @@
         <v>-7.142857142857</v>
       </c>
       <c r="N18" s="14">
-        <v>-89.763779527559</v>
+        <v>-90.647482014388</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,72 +1057,72 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D19" s="15">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>-9.090909090909</v>
+        <v>0</v>
       </c>
       <c r="F19" s="15">
         <v>27</v>
       </c>
       <c r="G19" s="15">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H19" s="14">
-        <v>3.846153846153</v>
+        <v>-6.896551724137</v>
       </c>
       <c r="I19" s="15">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J19" s="15">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K19" s="14">
-        <v>3.703703703703</v>
+        <v>1.666666666666</v>
       </c>
       <c r="L19" s="14">
-        <v>-26.315789473684</v>
+        <v>-25.609756097561</v>
       </c>
       <c r="M19" s="14">
-        <v>16.666666666666</v>
+        <v>22</v>
       </c>
       <c r="N19" s="14">
-        <v>-57.894736842105</v>
+        <v>-59.060402684563</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="15">
         <v>2</v>
       </c>
-      <c r="D20" s="15">
-        <v>1</v>
-      </c>
       <c r="E20" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="15">
         <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H20" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I20" s="15">
         <v>6</v>
       </c>
       <c r="J20" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K20" s="14">
-        <v>20</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L20" s="14">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>200</v>
       </c>
       <c r="N20" s="14">
-        <v>-93.684210526315</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>-9.523809523809</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="F21" s="17">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G21" s="17">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="H21" s="18">
-        <v>-1.851851851851</v>
+        <v>-14.754098360655</v>
       </c>
       <c r="I21" s="17">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="J21" s="17">
-        <v>131</v>
+        <v>145</v>
       </c>
       <c r="K21" s="18">
-        <v>-6.870229007633</v>
+        <v>-8.965517241379</v>
       </c>
       <c r="L21" s="18">
-        <v>-20.779220779220</v>
+        <v>-20</v>
       </c>
       <c r="M21" s="18">
-        <v>1.666666666666</v>
+        <v>3.125</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.819444444444</v>
+        <v>-79.277864992150</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,29 +1182,29 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="15">
+        <v>1</v>
+      </c>
+      <c r="E22" s="14">
+        <v>-100</v>
       </c>
       <c r="F22" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="15">
         <v>1</v>
       </c>
       <c r="H22" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I22" s="15">
         <v>4</v>
       </c>
       <c r="J22" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="14">
-        <v>-20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L22" s="14">
         <v>33.333333333333</v>
@@ -1230,28 +1230,28 @@
         <v>50</v>
       </c>
       <c r="F23" s="15">
+        <v>10</v>
+      </c>
+      <c r="G23" s="15">
         <v>9</v>
       </c>
-      <c r="G23" s="15">
-        <v>7</v>
-      </c>
       <c r="H23" s="14">
-        <v>28.571428571428</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I23" s="15">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J23" s="15">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K23" s="14">
-        <v>-4</v>
+        <v>-3.703703703703</v>
       </c>
       <c r="L23" s="14">
-        <v>-27.272727272727</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="M23" s="14">
-        <v>26.315789473684</v>
+        <v>23.809523809523</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D24" s="15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="E24" s="14">
-        <v>16.666666666666</v>
+        <v>-10</v>
       </c>
       <c r="F24" s="15">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G24" s="15">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H24" s="14">
-        <v>-41.860465116279</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I24" s="15">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J24" s="15">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="K24" s="14">
-        <v>-32.323232323232</v>
+        <v>-30.275229357798</v>
       </c>
       <c r="L24" s="14">
-        <v>-14.102564102564</v>
+        <v>-10.588235294117</v>
       </c>
       <c r="M24" s="14">
-        <v>-19.277108433734</v>
+        <v>-15.555555555555</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D25" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F25" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G25" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H25" s="14">
-        <v>-25</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I25" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J25" s="15">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K25" s="14">
-        <v>-28.571428571428</v>
+        <v>-29.411764705882</v>
       </c>
       <c r="L25" s="14">
-        <v>-28.571428571428</v>
+        <v>-20</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>300</v>
+        <v>125</v>
       </c>
       <c r="F26" s="15">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="G26" s="15">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H26" s="14">
-        <v>-23.809523809523</v>
+        <v>4.347826086956</v>
       </c>
       <c r="I26" s="15">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="J26" s="15">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="K26" s="14">
-        <v>-20.370370370370</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="L26" s="14">
-        <v>-27.118644067796</v>
+        <v>-18.75</v>
       </c>
       <c r="M26" s="14">
-        <v>-6.521739130434</v>
+        <v>0</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>1</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="15">
         <v>2</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="15">
-        <v>3</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D28" s="15">
+        <v>1</v>
+      </c>
+      <c r="E28" s="14">
+        <v>0</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="I28" s="15">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>140</v>
+        <v>116.666666666667</v>
       </c>
       <c r="L28" s="14">
-        <v>300</v>
+        <v>225</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1497,7 +1497,7 @@
         <v>21</v>
       </c>
       <c r="M29" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N29" s="14">
         <v>-80</v>
@@ -1538,7 +1538,7 @@
         <v>21</v>
       </c>
       <c r="M30" s="14">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N30" s="14">
         <v>-80</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="15">
+        <v>1</v>
+      </c>
+      <c r="E31" s="14">
+        <v>-100</v>
       </c>
       <c r="F31" s="15">
-        <v>2</v>
-      </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="G31" s="15">
+        <v>1</v>
+      </c>
+      <c r="H31" s="14">
+        <v>0</v>
       </c>
       <c r="I31" s="15">
         <v>3</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="15">
+        <v>1</v>
+      </c>
+      <c r="K31" s="14">
+        <v>200</v>
       </c>
       <c r="L31" s="14">
         <v>50</v>

--- a/data/source/weekly/cs-en-us-026pct.xlsx
+++ b/data/source/weekly/cs-en-us-026pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -895,38 +895,38 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="15">
-        <v>2</v>
+      <c r="D15" s="15">
+        <v>1</v>
+      </c>
+      <c r="E15" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="15">
         <v>2</v>
       </c>
       <c r="H15" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I15" s="15">
         <v>7</v>
       </c>
       <c r="J15" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K15" s="14">
+        <v>0</v>
+      </c>
+      <c r="L15" s="14">
+        <v>133.333333333333</v>
+      </c>
+      <c r="M15" s="14">
+        <v>75</v>
+      </c>
+      <c r="N15" s="14">
         <v>16.666666666666</v>
-      </c>
-      <c r="L15" s="14">
-        <v>250</v>
-      </c>
-      <c r="M15" s="14">
-        <v>133.333333333333</v>
-      </c>
-      <c r="N15" s="14">
-        <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,122 +934,122 @@
         <v>23</v>
       </c>
       <c r="C16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="14">
         <v>0</v>
       </c>
       <c r="F16" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H16" s="14">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I16" s="15">
         <v>14</v>
       </c>
       <c r="J16" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K16" s="14">
-        <v>-48.148148148148</v>
+        <v>-50</v>
       </c>
       <c r="L16" s="14">
-        <v>-53.333333333333</v>
+        <v>-56.25</v>
       </c>
       <c r="M16" s="14">
-        <v>-58.823529411764</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.178770949720</v>
+        <v>-92.432432432432</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>3</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="15">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="E17" s="14">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="15">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G17" s="15">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H17" s="14">
-        <v>10</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="I17" s="15">
         <v>31</v>
       </c>
       <c r="J17" s="15">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K17" s="14">
-        <v>6.896551724137</v>
+        <v>-8.823529411764</v>
       </c>
       <c r="L17" s="14">
-        <v>-6.060606060606</v>
+        <v>-20.512820512820</v>
       </c>
       <c r="M17" s="14">
-        <v>34.782608695652</v>
+        <v>24</v>
       </c>
       <c r="N17" s="14">
-        <v>-47.457627118644</v>
+        <v>-49.180327868852</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="15">
+        <v>1</v>
       </c>
       <c r="D18" s="15">
         <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="F18" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="14">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="I18" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J18" s="15">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K18" s="14">
-        <v>-18.75</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L18" s="14">
-        <v>8.333333333333</v>
+        <v>0</v>
       </c>
       <c r="M18" s="14">
-        <v>-7.142857142857</v>
+        <v>-12.5</v>
       </c>
       <c r="N18" s="14">
-        <v>-90.647482014388</v>
+        <v>-90.604026845637</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19" s="15">
         <v>6</v>
       </c>
       <c r="E19" s="14">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F19" s="15">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G19" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H19" s="14">
-        <v>-6.896551724137</v>
+        <v>-20</v>
       </c>
       <c r="I19" s="15">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J19" s="15">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K19" s="14">
-        <v>1.666666666666</v>
+        <v>-1.515151515151</v>
       </c>
       <c r="L19" s="14">
-        <v>-25.609756097561</v>
+        <v>-24.418604651162</v>
       </c>
       <c r="M19" s="14">
-        <v>22</v>
+        <v>18.181818181818</v>
       </c>
       <c r="N19" s="14">
-        <v>-59.060402684563</v>
+        <v>-59.876543209876</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,7 +1101,7 @@
         <v>20</v>
       </c>
       <c r="D20" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E20" s="14">
         <v>-100</v>
@@ -1110,19 +1110,19 @@
         <v>2</v>
       </c>
       <c r="G20" s="15">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H20" s="14">
-        <v>-66.666666666666</v>
+        <v>-77.777777777777</v>
       </c>
       <c r="I20" s="15">
         <v>6</v>
       </c>
       <c r="J20" s="15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K20" s="14">
-        <v>-14.285714285714</v>
+        <v>-40</v>
       </c>
       <c r="L20" s="14">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>200</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.117647058823</v>
+        <v>-94.495412844036</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-21.428571428571</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="G21" s="17">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="H21" s="18">
-        <v>-14.754098360655</v>
+        <v>-41.428571428571</v>
       </c>
       <c r="I21" s="17">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="J21" s="17">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="K21" s="18">
-        <v>-8.965517241379</v>
+        <v>-15.950920245398</v>
       </c>
       <c r="L21" s="18">
-        <v>-20</v>
+        <v>-23.888888888888</v>
       </c>
       <c r="M21" s="18">
-        <v>3.125</v>
+        <v>-2.142857142857</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.277864992150</v>
+        <v>-79.763663220088</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1192,25 +1192,25 @@
         <v>2</v>
       </c>
       <c r="G22" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I22" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J22" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="14">
-        <v>-33.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L22" s="14">
-        <v>33.333333333333</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M22" s="14">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>3</v>
+      <c r="C23" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D23" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E23" s="14">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="15">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G23" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H23" s="14">
-        <v>11.111111111111</v>
+        <v>-37.5</v>
       </c>
       <c r="I23" s="15">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J23" s="15">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K23" s="14">
-        <v>-3.703703703703</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="L23" s="14">
-        <v>-23.529411764705</v>
+        <v>-32.432432432432</v>
       </c>
       <c r="M23" s="14">
-        <v>23.809523809523</v>
+        <v>13.636363636363</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D24" s="15">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E24" s="14">
-        <v>-10</v>
+        <v>333.333333333333</v>
       </c>
       <c r="F24" s="15">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="G24" s="15">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="H24" s="14">
-        <v>-27.272727272727</v>
+        <v>23.529411764705</v>
       </c>
       <c r="I24" s="15">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="J24" s="15">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="K24" s="14">
-        <v>-30.275229357798</v>
+        <v>-19.642857142857</v>
       </c>
       <c r="L24" s="14">
-        <v>-10.588235294117</v>
+        <v>-1.098901098901</v>
       </c>
       <c r="M24" s="14">
-        <v>-15.555555555555</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1305,32 +1305,32 @@
       <c r="C25" s="15">
         <v>2</v>
       </c>
-      <c r="D25" s="15">
-        <v>3</v>
-      </c>
-      <c r="E25" s="14">
-        <v>-33.333333333333</v>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G25" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H25" s="14">
-        <v>-42.857142857142</v>
+        <v>20</v>
       </c>
       <c r="I25" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J25" s="15">
         <v>17</v>
       </c>
       <c r="K25" s="14">
-        <v>-29.411764705882</v>
+        <v>-17.647058823529</v>
       </c>
       <c r="L25" s="14">
-        <v>-20</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D26" s="15">
         <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="F26" s="15">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="G26" s="15">
         <v>23</v>
       </c>
       <c r="H26" s="14">
-        <v>4.347826086956</v>
+        <v>26.086956521739</v>
       </c>
       <c r="I26" s="15">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="J26" s="15">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="K26" s="14">
-        <v>-10.344827586206</v>
+        <v>-4.838709677419</v>
       </c>
       <c r="L26" s="14">
-        <v>-18.75</v>
+        <v>-14.492753623188</v>
       </c>
       <c r="M26" s="14">
-        <v>0</v>
+        <v>3.508771929824</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,32 +1387,32 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F27" s="15">
+      <c r="D27" s="15">
         <v>2</v>
       </c>
+      <c r="E27" s="14">
+        <v>-100</v>
+      </c>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G27" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H27" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I27" s="15">
         <v>7</v>
       </c>
       <c r="J27" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K27" s="14">
-        <v>0</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L27" s="14">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" s="15">
         <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="I28" s="15">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J28" s="15">
         <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>116.666666666667</v>
+        <v>133.333333333333</v>
       </c>
       <c r="L28" s="14">
-        <v>225</v>
+        <v>180</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1561,22 +1561,22 @@
         <v>1</v>
       </c>
       <c r="G31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I31" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K31" s="14">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="L31" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-026pct.xlsx
+++ b/data/source/weekly/cs-en-us-026pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -895,11 +895,11 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="15">
-        <v>1</v>
-      </c>
-      <c r="E15" s="14">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
@@ -926,7 +926,7 @@
         <v>75</v>
       </c>
       <c r="N15" s="14">
-        <v>16.666666666666</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -937,119 +937,119 @@
         <v>1</v>
       </c>
       <c r="D16" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F16" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G16" s="15">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>-66.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I16" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J16" s="15">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K16" s="14">
-        <v>-50</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="L16" s="14">
-        <v>-56.25</v>
+        <v>-54.285714285714</v>
       </c>
       <c r="M16" s="14">
-        <v>-61.111111111111</v>
+        <v>-58.974358974359</v>
       </c>
       <c r="N16" s="14">
-        <v>-92.432432432432</v>
+        <v>-91.959798994974</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="15">
+        <v>1</v>
       </c>
       <c r="D17" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E17" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F17" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G17" s="15">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="H17" s="14">
-        <v>-53.333333333333</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I17" s="15">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J17" s="15">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="K17" s="14">
-        <v>-8.823529411764</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="L17" s="14">
-        <v>-20.512820512820</v>
+        <v>-21.951219512195</v>
       </c>
       <c r="M17" s="14">
-        <v>24</v>
+        <v>18.518518518518</v>
       </c>
       <c r="N17" s="14">
-        <v>-49.180327868852</v>
+        <v>-52.941176470588</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="15">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="15">
         <v>2</v>
       </c>
       <c r="E18" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>0</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I18" s="15">
         <v>14</v>
       </c>
       <c r="J18" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K18" s="14">
-        <v>-22.222222222222</v>
+        <v>-30</v>
       </c>
       <c r="L18" s="14">
-        <v>0</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M18" s="14">
-        <v>-12.5</v>
+        <v>-26.315789473684</v>
       </c>
       <c r="N18" s="14">
-        <v>-90.604026845637</v>
+        <v>-91.139240506329</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,78 +1060,78 @@
         <v>4</v>
       </c>
       <c r="D19" s="15">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E19" s="14">
-        <v>-33.333333333333</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="F19" s="15">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G19" s="15">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="H19" s="14">
-        <v>-20</v>
+        <v>-32.352941176470</v>
       </c>
       <c r="I19" s="15">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="J19" s="15">
-        <v>66</v>
+        <v>77</v>
       </c>
       <c r="K19" s="14">
-        <v>-1.515151515151</v>
+        <v>-10.389610389610</v>
       </c>
       <c r="L19" s="14">
-        <v>-24.418604651162</v>
+        <v>-28.865979381443</v>
       </c>
       <c r="M19" s="14">
-        <v>18.181818181818</v>
+        <v>16.949152542372</v>
       </c>
       <c r="N19" s="14">
-        <v>-59.876543209876</v>
+        <v>-60.344827586206</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="15">
+        <v>1</v>
       </c>
       <c r="D20" s="15">
+        <v>2</v>
+      </c>
+      <c r="E20" s="14">
+        <v>-50</v>
+      </c>
+      <c r="F20" s="15">
         <v>3</v>
       </c>
-      <c r="E20" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F20" s="15">
-        <v>2</v>
-      </c>
       <c r="G20" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H20" s="14">
-        <v>-77.777777777777</v>
+        <v>-62.5</v>
       </c>
       <c r="I20" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J20" s="15">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K20" s="14">
-        <v>-40</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="L20" s="14">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
       <c r="M20" s="14">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.495412844036</v>
+        <v>-94.067796610169</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D21" s="17">
         <v>18</v>
       </c>
       <c r="E21" s="18">
-        <v>-66.666666666666</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="F21" s="17">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G21" s="17">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H21" s="18">
-        <v>-41.428571428571</v>
+        <v>-40.845070422535</v>
       </c>
       <c r="I21" s="17">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="J21" s="17">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="K21" s="18">
-        <v>-15.950920245398</v>
+        <v>-19.889502762430</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.888888888888</v>
+        <v>-27.135678391959</v>
       </c>
       <c r="M21" s="18">
-        <v>-2.142857142857</v>
+        <v>-4.605263157894</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.763663220088</v>
+        <v>-80.109739368998</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,20 +1182,20 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="15">
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F22" s="15">
         <v>1</v>
-      </c>
-      <c r="E22" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="15">
-        <v>2</v>
       </c>
       <c r="G22" s="15">
         <v>2</v>
       </c>
       <c r="H22" s="14">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I22" s="15">
         <v>5</v>
@@ -1207,7 +1207,7 @@
         <v>-28.571428571428</v>
       </c>
       <c r="L22" s="14">
-        <v>66.666666666666</v>
+        <v>25</v>
       </c>
       <c r="M22" s="14">
         <v>150</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="15">
+        <v>1</v>
       </c>
       <c r="D23" s="15">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E23" s="14">
-        <v>-100</v>
+        <v>-75</v>
       </c>
       <c r="F23" s="15">
         <v>5</v>
       </c>
       <c r="G23" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H23" s="14">
-        <v>-37.5</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="I23" s="15">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J23" s="15">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="K23" s="14">
-        <v>-10.714285714285</v>
+        <v>-18.75</v>
       </c>
       <c r="L23" s="14">
-        <v>-32.432432432432</v>
+        <v>-35</v>
       </c>
       <c r="M23" s="14">
-        <v>13.636363636363</v>
+        <v>4</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D24" s="15">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E24" s="14">
-        <v>333.333333333333</v>
+        <v>71.428571428571</v>
       </c>
       <c r="F24" s="15">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G24" s="15">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H24" s="14">
-        <v>23.529411764705</v>
+        <v>57.692307692307</v>
       </c>
       <c r="I24" s="15">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="J24" s="15">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="K24" s="14">
-        <v>-19.642857142857</v>
+        <v>-15.126050420168</v>
       </c>
       <c r="L24" s="14">
-        <v>-1.098901098901</v>
+        <v>6.315789473684</v>
       </c>
       <c r="M24" s="14">
-        <v>-11.764705882352</v>
+        <v>-6.481481481481</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1305,32 +1305,32 @@
       <c r="C25" s="15">
         <v>2</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+      <c r="D25" s="15">
+        <v>1</v>
+      </c>
+      <c r="E25" s="14">
+        <v>100</v>
       </c>
       <c r="F25" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G25" s="15">
         <v>5</v>
       </c>
       <c r="H25" s="14">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I25" s="15">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J25" s="15">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K25" s="14">
-        <v>-17.647058823529</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L25" s="14">
-        <v>-6.666666666666</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26" s="15">
         <v>4</v>
       </c>
       <c r="E26" s="14">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="F26" s="15">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G26" s="15">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="H26" s="14">
-        <v>26.086956521739</v>
+        <v>114.285714285714</v>
       </c>
       <c r="I26" s="15">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="J26" s="15">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="K26" s="14">
-        <v>-4.838709677419</v>
+        <v>-1.515151515151</v>
       </c>
       <c r="L26" s="14">
-        <v>-14.492753623188</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="M26" s="14">
-        <v>3.508771929824</v>
+        <v>12.068965517241</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,11 +1387,11 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="15">
-        <v>2</v>
-      </c>
-      <c r="E27" s="14">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G28" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H28" s="14">
-        <v>150</v>
+        <v>500</v>
       </c>
       <c r="I28" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J28" s="15">
         <v>6</v>
       </c>
       <c r="K28" s="14">
-        <v>133.333333333333</v>
+        <v>150</v>
       </c>
       <c r="L28" s="14">
-        <v>180</v>
+        <v>114.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,35 +1548,35 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="15">
+        <v>1</v>
       </c>
       <c r="D31" s="15">
         <v>1</v>
       </c>
       <c r="E31" s="14">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F31" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="14">
-        <v>-50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I31" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J31" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K31" s="14">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="L31" s="14">
-        <v>100</v>
+        <v>66.666666666666</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-026pct.xlsx
+++ b/data/source/weekly/cs-en-us-026pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -905,7 +905,7 @@
         <v>20</v>
       </c>
       <c r="G15" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="14">
         <v>-100</v>
@@ -920,7 +920,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="14">
-        <v>133.333333333333</v>
+        <v>75</v>
       </c>
       <c r="M15" s="14">
         <v>75</v>
@@ -933,82 +933,82 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="15">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="15">
         <v>2</v>
       </c>
       <c r="E16" s="14">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="15">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="15">
         <v>7</v>
       </c>
       <c r="H16" s="14">
-        <v>-28.571428571428</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I16" s="15">
         <v>16</v>
       </c>
       <c r="J16" s="15">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K16" s="14">
-        <v>-46.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L16" s="14">
-        <v>-54.285714285714</v>
+        <v>-58.974358974359</v>
       </c>
       <c r="M16" s="14">
-        <v>-58.974358974359</v>
+        <v>-61.904761904761</v>
       </c>
       <c r="N16" s="14">
-        <v>-91.959798994974</v>
+        <v>-92.233009708737</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="15">
-        <v>1</v>
+      <c r="C17" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D17" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E17" s="14">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="15">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G17" s="15">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="H17" s="14">
-        <v>-38.461538461538</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I17" s="15">
         <v>32</v>
       </c>
       <c r="J17" s="15">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K17" s="14">
-        <v>-8.571428571428</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L17" s="14">
-        <v>-21.951219512195</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="M17" s="14">
-        <v>18.518518518518</v>
+        <v>10.344827586206</v>
       </c>
       <c r="N17" s="14">
-        <v>-52.941176470588</v>
+        <v>-55.555555555555</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1019,37 +1019,37 @@
         <v>20</v>
       </c>
       <c r="D18" s="15">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="14">
         <v>-100</v>
       </c>
       <c r="F18" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" s="15">
         <v>7</v>
       </c>
       <c r="H18" s="14">
-        <v>-57.142857142857</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="I18" s="15">
         <v>14</v>
       </c>
       <c r="J18" s="15">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K18" s="14">
-        <v>-30</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L18" s="14">
         <v>-6.666666666666</v>
       </c>
       <c r="M18" s="14">
-        <v>-26.315789473684</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="N18" s="14">
-        <v>-91.139240506329</v>
+        <v>-91.764705882352</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D19" s="15">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="E19" s="14">
-        <v>-63.636363636363</v>
+        <v>-12.5</v>
       </c>
       <c r="F19" s="15">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G19" s="15">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="H19" s="14">
-        <v>-32.352941176470</v>
+        <v>-32.258064516129</v>
       </c>
       <c r="I19" s="15">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="J19" s="15">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="K19" s="14">
-        <v>-10.389610389610</v>
+        <v>-10.588235294117</v>
       </c>
       <c r="L19" s="14">
-        <v>-28.865979381443</v>
+        <v>-26.213592233009</v>
       </c>
       <c r="M19" s="14">
-        <v>16.949152542372</v>
+        <v>16.923076923076</v>
       </c>
       <c r="N19" s="14">
-        <v>-60.344827586206</v>
+        <v>-59.574468085106</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D20" s="15">
         <v>2</v>
       </c>
       <c r="E20" s="14">
-        <v>-50</v>
+        <v>0</v>
       </c>
       <c r="F20" s="15">
         <v>3</v>
       </c>
       <c r="G20" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H20" s="14">
-        <v>-62.5</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I20" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J20" s="15">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K20" s="14">
-        <v>-41.666666666666</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="L20" s="14">
-        <v>-12.5</v>
+        <v>12.5</v>
       </c>
       <c r="M20" s="14">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="N20" s="14">
-        <v>-94.067796610169</v>
+        <v>-92.913385826771</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D21" s="17">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E21" s="18">
-        <v>-61.111111111111</v>
+        <v>-43.75</v>
       </c>
       <c r="F21" s="17">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="G21" s="17">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="H21" s="18">
-        <v>-40.845070422535</v>
+        <v>-50</v>
       </c>
       <c r="I21" s="17">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="J21" s="17">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="K21" s="18">
-        <v>-19.889502762430</v>
+        <v>-21.827411167512</v>
       </c>
       <c r="L21" s="18">
-        <v>-27.135678391959</v>
+        <v>-28.372093023255</v>
       </c>
       <c r="M21" s="18">
-        <v>-4.605263157894</v>
+        <v>-8.875739644970</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.109739368998</v>
+        <v>-80.129032258064</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>25</v>
       </c>
       <c r="M22" s="14">
-        <v>150</v>
+        <v>66.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1224,34 +1224,34 @@
         <v>1</v>
       </c>
       <c r="D23" s="15">
+        <v>1</v>
+      </c>
+      <c r="E23" s="14">
+        <v>0</v>
+      </c>
+      <c r="F23" s="15">
         <v>4</v>
       </c>
-      <c r="E23" s="14">
-        <v>-75</v>
-      </c>
-      <c r="F23" s="15">
-        <v>5</v>
-      </c>
       <c r="G23" s="15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H23" s="14">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="15">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J23" s="15">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K23" s="14">
-        <v>-18.75</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L23" s="14">
-        <v>-35</v>
+        <v>-38.636363636363</v>
       </c>
       <c r="M23" s="14">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="15">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D24" s="15">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="E24" s="14">
-        <v>71.428571428571</v>
+        <v>25</v>
       </c>
       <c r="F24" s="15">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="G24" s="15">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H24" s="14">
-        <v>57.692307692307</v>
+        <v>58.333333333333</v>
       </c>
       <c r="I24" s="15">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="J24" s="15">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="K24" s="14">
-        <v>-15.126050420168</v>
+        <v>-14.634146341463</v>
       </c>
       <c r="L24" s="14">
-        <v>6.315789473684</v>
+        <v>0.961538461538</v>
       </c>
       <c r="M24" s="14">
-        <v>-6.481481481481</v>
+        <v>-13.934426229508</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="15">
+      <c r="C25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="15">
         <v>2</v>
       </c>
-      <c r="D25" s="15">
-        <v>1</v>
-      </c>
       <c r="E25" s="14">
-        <v>100</v>
+        <v>-100</v>
       </c>
       <c r="F25" s="15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G25" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H25" s="14">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="I25" s="15">
         <v>16</v>
       </c>
       <c r="J25" s="15">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="K25" s="14">
+        <v>-20</v>
+      </c>
+      <c r="L25" s="14">
         <v>-11.111111111111</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-5.882352941176</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="15">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="D26" s="15">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E26" s="14">
-        <v>100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F26" s="15">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G26" s="15">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H26" s="14">
-        <v>114.285714285714</v>
+        <v>60</v>
       </c>
       <c r="I26" s="15">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J26" s="15">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="K26" s="14">
-        <v>-1.515151515151</v>
+        <v>-2.898550724637</v>
       </c>
       <c r="L26" s="14">
-        <v>-7.142857142857</v>
+        <v>-15.189873417721</v>
       </c>
       <c r="M26" s="14">
-        <v>12.068965517241</v>
+        <v>13.559322033898</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1397,7 +1397,7 @@
         <v>20</v>
       </c>
       <c r="G27" s="15">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H27" s="14">
         <v>-100</v>
@@ -1412,7 +1412,7 @@
         <v>-22.222222222222</v>
       </c>
       <c r="L27" s="14">
-        <v>40</v>
+        <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="15">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="15">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="14">
+        <v>-100</v>
       </c>
       <c r="F28" s="15">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G28" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="14">
-        <v>500</v>
+        <v>50</v>
       </c>
       <c r="I28" s="15">
         <v>15</v>
       </c>
       <c r="J28" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K28" s="14">
-        <v>150</v>
+        <v>114.285714285714</v>
       </c>
       <c r="L28" s="14">
         <v>114.285714285714</v>
@@ -1497,7 +1497,7 @@
         <v>21</v>
       </c>
       <c r="M29" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N29" s="14">
         <v>-80</v>
@@ -1538,7 +1538,7 @@
         <v>21</v>
       </c>
       <c r="M30" s="14">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="N30" s="14">
         <v>-80</v>
@@ -1548,14 +1548,14 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="15">
-        <v>1</v>
-      </c>
-      <c r="D31" s="15">
-        <v>1</v>
-      </c>
-      <c r="E31" s="14">
-        <v>0</v>
+      <c r="C31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="15">
         <v>2</v>

--- a/data/source/weekly/cs-en-us-026pct.xlsx
+++ b/data/source/weekly/cs-en-us-026pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -329,8 +329,8 @@
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#0"/>
     <numFmt numFmtId="165" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
-    <numFmt numFmtId="167" formatCode="#,##0"/>
+    <numFmt numFmtId="166" formatCode="#,##0"/>
+    <numFmt numFmtId="167" formatCode="#,##0.0;&quot;-&quot;#,##0.0"/>
     <numFmt numFmtId="168" formatCode="#,##0.00;&quot;-&quot;#,##0.00"/>
   </numFmts>
   <fonts count="12">
@@ -546,7 +546,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -564,7 +564,7 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -854,37 +854,37 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="13" t="s">
-        <v>21</v>
+      <c r="J14" s="14">
+        <v>1</v>
+      </c>
+      <c r="K14" s="15">
+        <v>-100</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="14">
+      <c r="M14" s="15">
         <v>-100</v>
       </c>
-      <c r="N14" s="14">
+      <c r="N14" s="15">
         <v>-100</v>
       </c>
     </row>
@@ -895,37 +895,37 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="14">
+      <c r="G15" s="14">
+        <v>2</v>
+      </c>
+      <c r="H15" s="15">
         <v>-100</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="14">
         <v>7</v>
       </c>
-      <c r="J15" s="15">
-        <v>7</v>
-      </c>
-      <c r="K15" s="14">
-        <v>0</v>
-      </c>
-      <c r="L15" s="14">
+      <c r="J15" s="14">
+        <v>8</v>
+      </c>
+      <c r="K15" s="15">
+        <v>-12.5</v>
+      </c>
+      <c r="L15" s="15">
         <v>75</v>
       </c>
-      <c r="M15" s="14">
+      <c r="M15" s="15">
         <v>75</v>
       </c>
-      <c r="N15" s="14">
+      <c r="N15" s="15">
         <v>0</v>
       </c>
     </row>
@@ -933,82 +933,82 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="15">
+      <c r="C16" s="14">
         <v>2</v>
       </c>
-      <c r="E16" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F16" s="15">
-        <v>4</v>
-      </c>
-      <c r="G16" s="15">
-        <v>7</v>
-      </c>
-      <c r="H16" s="14">
-        <v>-42.857142857142</v>
-      </c>
-      <c r="I16" s="15">
-        <v>16</v>
-      </c>
-      <c r="J16" s="15">
-        <v>32</v>
-      </c>
-      <c r="K16" s="14">
-        <v>-50</v>
-      </c>
-      <c r="L16" s="14">
-        <v>-58.974358974359</v>
-      </c>
-      <c r="M16" s="14">
-        <v>-61.904761904761</v>
-      </c>
-      <c r="N16" s="14">
-        <v>-92.233009708737</v>
+      <c r="D16" s="14">
+        <v>1</v>
+      </c>
+      <c r="E16" s="15">
+        <v>100</v>
+      </c>
+      <c r="F16" s="14">
+        <v>5</v>
+      </c>
+      <c r="G16" s="14">
+        <v>6</v>
+      </c>
+      <c r="H16" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="I16" s="14">
+        <v>18</v>
+      </c>
+      <c r="J16" s="14">
+        <v>33</v>
+      </c>
+      <c r="K16" s="15">
+        <v>-45.454545454545</v>
+      </c>
+      <c r="L16" s="15">
+        <v>-57.142857142857</v>
+      </c>
+      <c r="M16" s="15">
+        <v>-63.265306122449</v>
+      </c>
+      <c r="N16" s="15">
+        <v>-91.743119266055</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D17" s="15">
+      <c r="C17" s="14">
+        <v>7</v>
+      </c>
+      <c r="D17" s="14">
         <v>3</v>
       </c>
-      <c r="E17" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F17" s="15">
-        <v>4</v>
-      </c>
-      <c r="G17" s="15">
-        <v>11</v>
-      </c>
-      <c r="H17" s="14">
-        <v>-63.636363636363</v>
-      </c>
-      <c r="I17" s="15">
-        <v>32</v>
-      </c>
-      <c r="J17" s="15">
-        <v>38</v>
-      </c>
-      <c r="K17" s="14">
-        <v>-15.789473684210</v>
-      </c>
-      <c r="L17" s="14">
-        <v>-30.434782608695</v>
-      </c>
-      <c r="M17" s="14">
-        <v>10.344827586206</v>
-      </c>
-      <c r="N17" s="14">
-        <v>-55.555555555555</v>
+      <c r="E17" s="15">
+        <v>133.333333333333</v>
+      </c>
+      <c r="F17" s="14">
+        <v>9</v>
+      </c>
+      <c r="G17" s="14">
+        <v>12</v>
+      </c>
+      <c r="H17" s="15">
+        <v>-25</v>
+      </c>
+      <c r="I17" s="14">
+        <v>40</v>
+      </c>
+      <c r="J17" s="14">
+        <v>41</v>
+      </c>
+      <c r="K17" s="15">
+        <v>-2.439024390243</v>
+      </c>
+      <c r="L17" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="M17" s="15">
+        <v>25</v>
+      </c>
+      <c r="N17" s="15">
+        <v>-46.666666666666</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,120 +1018,120 @@
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="15">
-        <v>1</v>
-      </c>
-      <c r="E18" s="14">
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
         <v>-100</v>
       </c>
-      <c r="F18" s="15">
-        <v>1</v>
-      </c>
-      <c r="G18" s="15">
-        <v>7</v>
-      </c>
-      <c r="H18" s="14">
-        <v>-85.714285714285</v>
-      </c>
-      <c r="I18" s="15">
+      <c r="F18" s="14">
+        <v>1</v>
+      </c>
+      <c r="G18" s="14">
+        <v>6</v>
+      </c>
+      <c r="H18" s="15">
+        <v>-83.333333333333</v>
+      </c>
+      <c r="I18" s="14">
         <v>14</v>
       </c>
-      <c r="J18" s="15">
-        <v>21</v>
-      </c>
-      <c r="K18" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="L18" s="14">
+      <c r="J18" s="14">
+        <v>22</v>
+      </c>
+      <c r="K18" s="15">
+        <v>-36.363636363636</v>
+      </c>
+      <c r="L18" s="15">
         <v>-6.666666666666</v>
       </c>
-      <c r="M18" s="14">
-        <v>-41.666666666666</v>
-      </c>
-      <c r="N18" s="14">
-        <v>-91.764705882352</v>
+      <c r="M18" s="15">
+        <v>-44</v>
+      </c>
+      <c r="N18" s="15">
+        <v>-92.631578947368</v>
       </c>
     </row>
     <row r="19" spans="1:14">
       <c r="A19" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="15">
-        <v>7</v>
-      </c>
-      <c r="D19" s="15">
+      <c r="C19" s="14">
         <v>8</v>
       </c>
-      <c r="E19" s="14">
-        <v>-12.5</v>
-      </c>
-      <c r="F19" s="15">
-        <v>21</v>
-      </c>
-      <c r="G19" s="15">
-        <v>31</v>
-      </c>
-      <c r="H19" s="14">
-        <v>-32.258064516129</v>
-      </c>
-      <c r="I19" s="15">
-        <v>76</v>
-      </c>
-      <c r="J19" s="15">
-        <v>85</v>
-      </c>
-      <c r="K19" s="14">
-        <v>-10.588235294117</v>
-      </c>
-      <c r="L19" s="14">
-        <v>-26.213592233009</v>
-      </c>
-      <c r="M19" s="14">
-        <v>16.923076923076</v>
-      </c>
-      <c r="N19" s="14">
-        <v>-59.574468085106</v>
+      <c r="D19" s="14">
+        <v>9</v>
+      </c>
+      <c r="E19" s="15">
+        <v>-11.111111111111</v>
+      </c>
+      <c r="F19" s="14">
+        <v>21</v>
+      </c>
+      <c r="G19" s="14">
+        <v>34</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-38.235294117647</v>
+      </c>
+      <c r="I19" s="14">
+        <v>82</v>
+      </c>
+      <c r="J19" s="14">
+        <v>94</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-12.765957446808</v>
+      </c>
+      <c r="L19" s="15">
+        <v>-26.785714285714</v>
+      </c>
+      <c r="M19" s="15">
+        <v>12.328767123287</v>
+      </c>
+      <c r="N19" s="15">
+        <v>-59.803921568627</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="15">
-        <v>2</v>
-      </c>
-      <c r="D20" s="15">
-        <v>2</v>
-      </c>
-      <c r="E20" s="14">
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F20" s="14">
+        <v>3</v>
+      </c>
+      <c r="G20" s="14">
+        <v>8</v>
+      </c>
+      <c r="H20" s="15">
+        <v>-62.5</v>
+      </c>
+      <c r="I20" s="14">
+        <v>9</v>
+      </c>
+      <c r="J20" s="14">
+        <v>15</v>
+      </c>
+      <c r="K20" s="15">
+        <v>-40</v>
+      </c>
+      <c r="L20" s="15">
         <v>0</v>
       </c>
-      <c r="F20" s="15">
-        <v>3</v>
-      </c>
-      <c r="G20" s="15">
-        <v>9</v>
-      </c>
-      <c r="H20" s="14">
-        <v>-66.666666666666</v>
-      </c>
-      <c r="I20" s="15">
-        <v>9</v>
-      </c>
-      <c r="J20" s="15">
-        <v>14</v>
-      </c>
-      <c r="K20" s="14">
-        <v>-35.714285714285</v>
-      </c>
-      <c r="L20" s="14">
-        <v>12.5</v>
-      </c>
-      <c r="M20" s="14">
-        <v>200</v>
-      </c>
-      <c r="N20" s="14">
-        <v>-92.913385826771</v>
+      <c r="M20" s="15">
+        <v>125</v>
+      </c>
+      <c r="N20" s="15">
+        <v>-93.076923076923</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>-43.75</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="G21" s="17">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H21" s="18">
-        <v>-50</v>
+        <v>-43.478260869565</v>
       </c>
       <c r="I21" s="17">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="J21" s="17">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.827411167512</v>
+        <v>-20.560747663551</v>
       </c>
       <c r="L21" s="18">
-        <v>-28.372093023255</v>
+        <v>-26.086956521739</v>
       </c>
       <c r="M21" s="18">
-        <v>-8.875739644970</v>
+        <v>-10.052910052910</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.129032258064</v>
+        <v>-79.493365500603</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="15">
-        <v>1</v>
-      </c>
-      <c r="G22" s="15">
+      <c r="C22" s="14">
+        <v>1</v>
+      </c>
+      <c r="D22" s="14">
+        <v>1</v>
+      </c>
+      <c r="E22" s="15">
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
+      </c>
+      <c r="G22" s="14">
         <v>2</v>
       </c>
-      <c r="H22" s="14">
+      <c r="H22" s="15">
         <v>-50</v>
       </c>
-      <c r="I22" s="15">
-        <v>5</v>
-      </c>
-      <c r="J22" s="15">
-        <v>7</v>
-      </c>
-      <c r="K22" s="14">
-        <v>-28.571428571428</v>
-      </c>
-      <c r="L22" s="14">
-        <v>25</v>
-      </c>
-      <c r="M22" s="14">
-        <v>66.666666666666</v>
+      <c r="I22" s="14">
+        <v>6</v>
+      </c>
+      <c r="J22" s="14">
+        <v>8</v>
+      </c>
+      <c r="K22" s="15">
+        <v>-25</v>
+      </c>
+      <c r="L22" s="15">
+        <v>20</v>
+      </c>
+      <c r="M22" s="15">
+        <v>50</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="15">
-        <v>1</v>
-      </c>
-      <c r="D23" s="15">
-        <v>1</v>
-      </c>
-      <c r="E23" s="14">
-        <v>0</v>
-      </c>
-      <c r="F23" s="15">
-        <v>4</v>
-      </c>
-      <c r="G23" s="15">
-        <v>8</v>
-      </c>
-      <c r="H23" s="14">
-        <v>-50</v>
-      </c>
-      <c r="I23" s="15">
-        <v>27</v>
-      </c>
-      <c r="J23" s="15">
-        <v>33</v>
-      </c>
-      <c r="K23" s="14">
-        <v>-18.181818181818</v>
-      </c>
-      <c r="L23" s="14">
-        <v>-38.636363636363</v>
-      </c>
-      <c r="M23" s="14">
-        <v>0</v>
+      <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
+        <v>5</v>
+      </c>
+      <c r="E23" s="15">
+        <v>-80</v>
+      </c>
+      <c r="F23" s="14">
+        <v>3</v>
+      </c>
+      <c r="G23" s="14">
+        <v>11</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-72.727272727272</v>
+      </c>
+      <c r="I23" s="14">
+        <v>28</v>
+      </c>
+      <c r="J23" s="14">
+        <v>38</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-26.315789473684</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-39.130434782608</v>
+      </c>
+      <c r="M23" s="15">
+        <v>3.703703703703</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1261,38 +1261,38 @@
       <c r="A24" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="15">
-        <v>5</v>
-      </c>
-      <c r="D24" s="15">
-        <v>4</v>
-      </c>
-      <c r="E24" s="14">
-        <v>25</v>
-      </c>
-      <c r="F24" s="15">
-        <v>38</v>
-      </c>
-      <c r="G24" s="15">
-        <v>24</v>
-      </c>
-      <c r="H24" s="14">
-        <v>58.333333333333</v>
-      </c>
-      <c r="I24" s="15">
-        <v>105</v>
-      </c>
-      <c r="J24" s="15">
-        <v>123</v>
-      </c>
-      <c r="K24" s="14">
-        <v>-14.634146341463</v>
-      </c>
-      <c r="L24" s="14">
-        <v>0.961538461538</v>
-      </c>
-      <c r="M24" s="14">
-        <v>-13.934426229508</v>
+      <c r="C24" s="14">
+        <v>14</v>
+      </c>
+      <c r="D24" s="14">
+        <v>14</v>
+      </c>
+      <c r="E24" s="15">
+        <v>0</v>
+      </c>
+      <c r="F24" s="14">
+        <v>43</v>
+      </c>
+      <c r="G24" s="14">
+        <v>28</v>
+      </c>
+      <c r="H24" s="15">
+        <v>53.571428571428</v>
+      </c>
+      <c r="I24" s="14">
+        <v>119</v>
+      </c>
+      <c r="J24" s="14">
+        <v>137</v>
+      </c>
+      <c r="K24" s="15">
+        <v>-13.138686131386</v>
+      </c>
+      <c r="L24" s="15">
+        <v>5.309734513274</v>
+      </c>
+      <c r="M24" s="15">
+        <v>-9.848484848484</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="15">
+      <c r="C25" s="14">
+        <v>4</v>
+      </c>
+      <c r="D25" s="14">
         <v>2</v>
       </c>
-      <c r="E25" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F25" s="15">
-        <v>6</v>
-      </c>
-      <c r="G25" s="15">
-        <v>6</v>
-      </c>
-      <c r="H25" s="14">
-        <v>0</v>
-      </c>
-      <c r="I25" s="15">
-        <v>16</v>
-      </c>
-      <c r="J25" s="15">
-        <v>20</v>
-      </c>
-      <c r="K25" s="14">
-        <v>-20</v>
-      </c>
-      <c r="L25" s="14">
-        <v>-11.111111111111</v>
+      <c r="E25" s="15">
+        <v>100</v>
+      </c>
+      <c r="F25" s="14">
+        <v>8</v>
+      </c>
+      <c r="G25" s="14">
+        <v>5</v>
+      </c>
+      <c r="H25" s="15">
+        <v>60</v>
+      </c>
+      <c r="I25" s="14">
+        <v>20</v>
+      </c>
+      <c r="J25" s="14">
+        <v>22</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-9.090909090909</v>
+      </c>
+      <c r="L25" s="15">
+        <v>11.111111111111</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1343,38 +1343,38 @@
       <c r="A26" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="C26" s="15">
-        <v>2</v>
-      </c>
-      <c r="D26" s="15">
+      <c r="C26" s="14">
+        <v>4</v>
+      </c>
+      <c r="D26" s="14">
         <v>3</v>
       </c>
-      <c r="E26" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F26" s="15">
-        <v>24</v>
-      </c>
-      <c r="G26" s="15">
-        <v>15</v>
-      </c>
-      <c r="H26" s="14">
-        <v>60</v>
-      </c>
-      <c r="I26" s="15">
-        <v>67</v>
-      </c>
-      <c r="J26" s="15">
-        <v>69</v>
-      </c>
-      <c r="K26" s="14">
-        <v>-2.898550724637</v>
-      </c>
-      <c r="L26" s="14">
-        <v>-15.189873417721</v>
-      </c>
-      <c r="M26" s="14">
-        <v>13.559322033898</v>
+      <c r="E26" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="F26" s="14">
+        <v>18</v>
+      </c>
+      <c r="G26" s="14">
+        <v>14</v>
+      </c>
+      <c r="H26" s="15">
+        <v>28.571428571428</v>
+      </c>
+      <c r="I26" s="14">
+        <v>71</v>
+      </c>
+      <c r="J26" s="14">
+        <v>72</v>
+      </c>
+      <c r="K26" s="15">
+        <v>-1.388888888888</v>
+      </c>
+      <c r="L26" s="15">
+        <v>-14.457831325301</v>
+      </c>
+      <c r="M26" s="15">
+        <v>7.575757575757</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,31 +1387,31 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="15">
-        <v>2</v>
-      </c>
-      <c r="H27" s="14">
+      <c r="G27" s="14">
+        <v>3</v>
+      </c>
+      <c r="H27" s="15">
         <v>-100</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="14">
         <v>7</v>
       </c>
-      <c r="J27" s="15">
-        <v>9</v>
-      </c>
-      <c r="K27" s="14">
-        <v>-22.222222222222</v>
-      </c>
-      <c r="L27" s="14">
+      <c r="J27" s="14">
+        <v>10</v>
+      </c>
+      <c r="K27" s="15">
+        <v>-30</v>
+      </c>
+      <c r="L27" s="15">
         <v>16.666666666666</v>
       </c>
       <c r="M27" s="13" t="s">
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15">
-        <v>1</v>
-      </c>
-      <c r="E28" s="14">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="15">
+      <c r="C28" s="14">
+        <v>1</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>3</v>
       </c>
-      <c r="G28" s="15">
-        <v>2</v>
-      </c>
-      <c r="H28" s="14">
-        <v>50</v>
-      </c>
-      <c r="I28" s="15">
-        <v>15</v>
-      </c>
-      <c r="J28" s="15">
+      <c r="G28" s="14">
+        <v>1</v>
+      </c>
+      <c r="H28" s="15">
+        <v>200</v>
+      </c>
+      <c r="I28" s="14">
+        <v>16</v>
+      </c>
+      <c r="J28" s="14">
         <v>7</v>
       </c>
-      <c r="K28" s="14">
-        <v>114.285714285714</v>
-      </c>
-      <c r="L28" s="14">
-        <v>114.285714285714</v>
+      <c r="K28" s="15">
+        <v>128.571428571429</v>
+      </c>
+      <c r="L28" s="15">
+        <v>128.571428571429</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,37 +1469,37 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I29" s="15">
-        <v>1</v>
-      </c>
-      <c r="J29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
+      </c>
+      <c r="I29" s="14">
+        <v>1</v>
+      </c>
+      <c r="J29" s="14">
+        <v>1</v>
+      </c>
+      <c r="K29" s="15">
+        <v>0</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M29" s="14">
+      <c r="M29" s="15">
         <v>-75</v>
       </c>
-      <c r="N29" s="14">
+      <c r="N29" s="15">
         <v>-80</v>
       </c>
     </row>
@@ -1510,37 +1510,37 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I30" s="15">
-        <v>1</v>
-      </c>
-      <c r="J30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
+      </c>
+      <c r="I30" s="14">
+        <v>1</v>
+      </c>
+      <c r="J30" s="14">
+        <v>1</v>
+      </c>
+      <c r="K30" s="15">
+        <v>0</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M30" s="14">
+      <c r="M30" s="15">
         <v>-75</v>
       </c>
-      <c r="N30" s="14">
+      <c r="N30" s="15">
         <v>-80</v>
       </c>
     </row>
@@ -1557,26 +1557,26 @@
       <c r="E31" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F31" s="15">
+      <c r="F31" s="14">
         <v>2</v>
       </c>
-      <c r="G31" s="15">
+      <c r="G31" s="14">
+        <v>2</v>
+      </c>
+      <c r="H31" s="15">
+        <v>0</v>
+      </c>
+      <c r="I31" s="14">
+        <v>6</v>
+      </c>
+      <c r="J31" s="14">
         <v>3</v>
       </c>
-      <c r="H31" s="14">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="I31" s="15">
-        <v>5</v>
-      </c>
-      <c r="J31" s="15">
-        <v>3</v>
-      </c>
-      <c r="K31" s="14">
-        <v>66.666666666666</v>
-      </c>
-      <c r="L31" s="14">
-        <v>66.666666666666</v>
+      <c r="K31" s="15">
+        <v>100</v>
+      </c>
+      <c r="L31" s="15">
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
@@ -1742,31 +1742,31 @@
       <c r="A39" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C39" s="15">
+      <c r="C39" s="14">
         <v>15</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="14">
         <v>14</v>
       </c>
-      <c r="G39" s="15">
+      <c r="G39" s="14">
         <v>3</v>
       </c>
-      <c r="I39" s="15">
-        <v>1</v>
-      </c>
-      <c r="J39" s="15">
+      <c r="I39" s="14">
+        <v>1</v>
+      </c>
+      <c r="J39" s="14">
         <v>2</v>
       </c>
-      <c r="K39" s="14">
+      <c r="K39" s="15">
         <v>100</v>
       </c>
-      <c r="L39" s="14">
+      <c r="L39" s="15">
         <v>-33.333333333333</v>
       </c>
-      <c r="M39" s="14">
+      <c r="M39" s="15">
         <v>-85.714285714285</v>
       </c>
-      <c r="N39" s="14">
+      <c r="N39" s="15">
         <v>-86.666666666666</v>
       </c>
     </row>
@@ -1774,31 +1774,31 @@
       <c r="A40" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C40" s="15">
+      <c r="C40" s="14">
         <v>23</v>
       </c>
-      <c r="E40" s="15">
+      <c r="E40" s="14">
         <v>26</v>
       </c>
-      <c r="G40" s="15">
+      <c r="G40" s="14">
         <v>16</v>
       </c>
-      <c r="I40" s="15">
+      <c r="I40" s="14">
         <v>9</v>
       </c>
-      <c r="J40" s="15">
+      <c r="J40" s="14">
         <v>22</v>
       </c>
-      <c r="K40" s="14">
+      <c r="K40" s="15">
         <v>144.444444444444</v>
       </c>
-      <c r="L40" s="14">
+      <c r="L40" s="15">
         <v>37.5</v>
       </c>
-      <c r="M40" s="14">
+      <c r="M40" s="15">
         <v>-15.384615384615</v>
       </c>
-      <c r="N40" s="14">
+      <c r="N40" s="15">
         <v>-4.347826086956</v>
       </c>
     </row>
@@ -1806,31 +1806,31 @@
       <c r="A41" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C41" s="15">
+      <c r="C41" s="14">
         <v>786</v>
       </c>
-      <c r="E41" s="15">
+      <c r="E41" s="14">
         <v>772</v>
       </c>
-      <c r="G41" s="15">
+      <c r="G41" s="14">
         <v>339</v>
       </c>
-      <c r="I41" s="15">
+      <c r="I41" s="14">
         <v>220</v>
       </c>
-      <c r="J41" s="15">
+      <c r="J41" s="14">
         <v>91</v>
       </c>
-      <c r="K41" s="14">
+      <c r="K41" s="15">
         <v>-58.636363636363</v>
       </c>
-      <c r="L41" s="14">
+      <c r="L41" s="15">
         <v>-73.156342182890</v>
       </c>
-      <c r="M41" s="14">
+      <c r="M41" s="15">
         <v>-88.212435233160</v>
       </c>
-      <c r="N41" s="14">
+      <c r="N41" s="15">
         <v>-88.422391857506</v>
       </c>
     </row>
@@ -1838,31 +1838,31 @@
       <c r="A42" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C42" s="15">
+      <c r="C42" s="14">
         <v>315</v>
       </c>
-      <c r="E42" s="15">
+      <c r="E42" s="14">
         <v>290</v>
       </c>
-      <c r="G42" s="15">
+      <c r="G42" s="14">
         <v>198</v>
       </c>
-      <c r="I42" s="15">
+      <c r="I42" s="14">
         <v>132</v>
       </c>
-      <c r="J42" s="15">
+      <c r="J42" s="14">
         <v>163</v>
       </c>
-      <c r="K42" s="14">
+      <c r="K42" s="15">
         <v>23.484848484848</v>
       </c>
-      <c r="L42" s="14">
+      <c r="L42" s="15">
         <v>-17.676767676767</v>
       </c>
-      <c r="M42" s="14">
+      <c r="M42" s="15">
         <v>-43.793103448275</v>
       </c>
-      <c r="N42" s="14">
+      <c r="N42" s="15">
         <v>-48.253968253968</v>
       </c>
     </row>
@@ -1870,31 +1870,31 @@
       <c r="A43" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C43" s="15">
+      <c r="C43" s="14">
         <v>807</v>
       </c>
-      <c r="E43" s="15">
+      <c r="E43" s="14">
         <v>624</v>
       </c>
-      <c r="G43" s="15">
+      <c r="G43" s="14">
         <v>271</v>
       </c>
-      <c r="I43" s="15">
+      <c r="I43" s="14">
         <v>124</v>
       </c>
-      <c r="J43" s="15">
+      <c r="J43" s="14">
         <v>53</v>
       </c>
-      <c r="K43" s="14">
+      <c r="K43" s="15">
         <v>-57.258064516129</v>
       </c>
-      <c r="L43" s="14">
+      <c r="L43" s="15">
         <v>-80.442804428044</v>
       </c>
-      <c r="M43" s="14">
+      <c r="M43" s="15">
         <v>-91.506410256410</v>
       </c>
-      <c r="N43" s="14">
+      <c r="N43" s="15">
         <v>-93.432465923172</v>
       </c>
     </row>
@@ -1902,31 +1902,31 @@
       <c r="A44" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="C44" s="15">
+      <c r="C44" s="14">
         <v>798</v>
       </c>
-      <c r="E44" s="15">
+      <c r="E44" s="14">
         <v>663</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="14">
         <v>386</v>
       </c>
-      <c r="I44" s="15">
+      <c r="I44" s="14">
         <v>326</v>
       </c>
-      <c r="J44" s="15">
+      <c r="J44" s="14">
         <v>381</v>
       </c>
-      <c r="K44" s="14">
+      <c r="K44" s="15">
         <v>16.871165644171</v>
       </c>
-      <c r="L44" s="14">
+      <c r="L44" s="15">
         <v>-1.295336787564</v>
       </c>
-      <c r="M44" s="14">
+      <c r="M44" s="15">
         <v>-42.533936651583</v>
       </c>
-      <c r="N44" s="14">
+      <c r="N44" s="15">
         <v>-52.255639097744</v>
       </c>
     </row>
@@ -1934,31 +1934,31 @@
       <c r="A45" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C45" s="15">
+      <c r="C45" s="14">
         <v>636</v>
       </c>
-      <c r="E45" s="15">
+      <c r="E45" s="14">
         <v>360</v>
       </c>
-      <c r="G45" s="15">
+      <c r="G45" s="14">
         <v>114</v>
       </c>
-      <c r="I45" s="15">
+      <c r="I45" s="14">
         <v>133</v>
       </c>
-      <c r="J45" s="15">
+      <c r="J45" s="14">
         <v>48</v>
       </c>
-      <c r="K45" s="14">
+      <c r="K45" s="15">
         <v>-63.909774436090</v>
       </c>
-      <c r="L45" s="14">
+      <c r="L45" s="15">
         <v>-57.894736842105</v>
       </c>
-      <c r="M45" s="14">
+      <c r="M45" s="15">
         <v>-86.666666666666</v>
       </c>
-      <c r="N45" s="14">
+      <c r="N45" s="15">
         <v>-92.452830188679</v>
       </c>
     </row>

--- a/data/source/weekly/cs-en-us-026pct.xlsx
+++ b/data/source/weekly/cs-en-us-026pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -895,17 +895,17 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G15" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H15" s="15">
         <v>-100</v>
@@ -926,7 +926,7 @@
         <v>75</v>
       </c>
       <c r="N15" s="15">
-        <v>0</v>
+        <v>-12.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
         <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" s="14">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="K16" s="15">
-        <v>-45.454545454545</v>
+        <v>-44.117647058823</v>
       </c>
       <c r="L16" s="15">
-        <v>-57.142857142857</v>
+        <v>-59.574468085106</v>
       </c>
       <c r="M16" s="15">
-        <v>-63.265306122449</v>
+        <v>-63.461538461538</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.743119266055</v>
+        <v>-91.949152542372</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
         <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>133.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H17" s="15">
-        <v>-25</v>
+        <v>30</v>
       </c>
       <c r="I17" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J17" s="14">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="K17" s="15">
-        <v>-2.439024390243</v>
+        <v>0</v>
       </c>
       <c r="L17" s="15">
-        <v>-16.666666666666</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M17" s="15">
-        <v>25</v>
+        <v>37.5</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.666666666666</v>
+        <v>-46.341463414634</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="14">
-        <v>1</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-100</v>
+      <c r="C18" s="14">
+        <v>3</v>
+      </c>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>-83.333333333333</v>
+        <v>-25</v>
       </c>
       <c r="I18" s="14">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J18" s="14">
         <v>22</v>
       </c>
       <c r="K18" s="15">
-        <v>-36.363636363636</v>
+        <v>-22.727272727272</v>
       </c>
       <c r="L18" s="15">
-        <v>-6.666666666666</v>
+        <v>13.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-44</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.631578947368</v>
+        <v>-91.707317073170</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>-11.111111111111</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G19" s="14">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H19" s="15">
-        <v>-38.235294117647</v>
+        <v>-31.428571428571</v>
       </c>
       <c r="I19" s="14">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="J19" s="14">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="K19" s="15">
-        <v>-12.765957446808</v>
+        <v>-11.881188118811</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.785714285714</v>
+        <v>-24.576271186440</v>
       </c>
       <c r="M19" s="15">
-        <v>12.328767123287</v>
+        <v>17.105263157894</v>
       </c>
       <c r="N19" s="15">
-        <v>-59.803921568627</v>
+        <v>-59.545454545454</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>-100</v>
+      <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>-62.5</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="J20" s="14">
         <v>15</v>
       </c>
       <c r="K20" s="15">
-        <v>-40</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M20" s="15">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="N20" s="15">
-        <v>-93.076923076923</v>
+        <v>-91.970802919708</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,37 +1142,37 @@
         <v>17</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>54.545454545454</v>
       </c>
       <c r="F21" s="17">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="G21" s="17">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="H21" s="18">
-        <v>-43.478260869565</v>
+        <v>-20.967741935483</v>
       </c>
       <c r="I21" s="17">
-        <v>170</v>
+        <v>187</v>
       </c>
       <c r="J21" s="17">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.560747663551</v>
+        <v>-16.888888888888</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.086956521739</v>
+        <v>-23.983739837398</v>
       </c>
       <c r="M21" s="18">
-        <v>-10.052910052910</v>
+        <v>-5.076142131979</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.493365500603</v>
+        <v>-79.059350503919</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>-50</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="14">
         <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>-25</v>
+        <v>-12.5</v>
       </c>
       <c r="L22" s="15">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M22" s="15">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1223,35 +1223,35 @@
       <c r="C23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="14">
-        <v>5</v>
-      </c>
-      <c r="E23" s="15">
-        <v>-80</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>-72.727272727272</v>
+        <v>-60</v>
       </c>
       <c r="I23" s="14">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J23" s="14">
         <v>38</v>
       </c>
       <c r="K23" s="15">
-        <v>-26.315789473684</v>
+        <v>-23.684210526315</v>
       </c>
       <c r="L23" s="15">
-        <v>-39.130434782608</v>
+        <v>-38.297872340425</v>
       </c>
       <c r="M23" s="15">
-        <v>3.703703703703</v>
+        <v>7.407407407407</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="E24" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F24" s="14">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G24" s="14">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="H24" s="15">
-        <v>53.571428571428</v>
+        <v>20</v>
       </c>
       <c r="I24" s="14">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="J24" s="14">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="K24" s="15">
-        <v>-13.138686131386</v>
+        <v>-11.564625850340</v>
       </c>
       <c r="L24" s="15">
-        <v>5.309734513274</v>
+        <v>6.557377049180</v>
       </c>
       <c r="M24" s="15">
-        <v>-9.848484848484</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
+        <v>7</v>
+      </c>
+      <c r="G25" s="14">
         <v>8</v>
       </c>
-      <c r="G25" s="14">
+      <c r="H25" s="15">
+        <v>-12.5</v>
+      </c>
+      <c r="I25" s="14">
+        <v>21</v>
+      </c>
+      <c r="J25" s="14">
+        <v>25</v>
+      </c>
+      <c r="K25" s="15">
+        <v>-16</v>
+      </c>
+      <c r="L25" s="15">
         <v>5</v>
-      </c>
-      <c r="H25" s="15">
-        <v>60</v>
-      </c>
-      <c r="I25" s="14">
-        <v>20</v>
-      </c>
-      <c r="J25" s="14">
-        <v>22</v>
-      </c>
-      <c r="K25" s="15">
-        <v>-9.090909090909</v>
-      </c>
-      <c r="L25" s="15">
-        <v>11.111111111111</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>33.333333333333</v>
+        <v>-54.545454545454</v>
       </c>
       <c r="F26" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G26" s="14">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="H26" s="15">
-        <v>28.571428571428</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I26" s="14">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="J26" s="14">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="K26" s="15">
-        <v>-1.388888888888</v>
+        <v>-8.433734939759</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.457831325301</v>
+        <v>-12.643678160919</v>
       </c>
       <c r="M26" s="15">
-        <v>7.575757575757</v>
+        <v>2.702702702702</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,17 +1387,17 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G27" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H27" s="15">
         <v>-100</v>
@@ -1428,29 +1428,29 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H28" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I28" s="14">
         <v>16</v>
       </c>
       <c r="J28" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>128.571428571429</v>
+        <v>100</v>
       </c>
       <c r="L28" s="15">
         <v>128.571428571429</v>
@@ -1466,82 +1466,82 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
+      </c>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="14">
         <v>1</v>
       </c>
       <c r="H29" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J29" s="14">
         <v>1</v>
       </c>
       <c r="K29" s="15">
-        <v>0</v>
-      </c>
-      <c r="L29" s="13" t="s">
-        <v>21</v>
+        <v>100</v>
+      </c>
+      <c r="L29" s="15">
+        <v>100</v>
       </c>
       <c r="M29" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="N29" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
+      </c>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="14">
         <v>1</v>
       </c>
       <c r="H30" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="I30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J30" s="14">
         <v>1</v>
       </c>
       <c r="K30" s="15">
-        <v>0</v>
-      </c>
-      <c r="L30" s="13" t="s">
-        <v>21</v>
+        <v>100</v>
+      </c>
+      <c r="L30" s="15">
+        <v>100</v>
       </c>
       <c r="M30" s="15">
-        <v>-75</v>
+        <v>-50</v>
       </c>
       <c r="N30" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,32 +1551,32 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G31" s="14">
         <v>2</v>
       </c>
       <c r="H31" s="15">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="I31" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="L31" s="15">
-        <v>100</v>
+        <v>75</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-026pct.xlsx
+++ b/data/source/weekly/cs-en-us-026pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="14">
-        <v>1</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
+        <v>5</v>
+      </c>
+      <c r="G16" s="14">
         <v>4</v>
       </c>
-      <c r="G16" s="14">
-        <v>6</v>
-      </c>
       <c r="H16" s="15">
-        <v>-33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="I16" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J16" s="14">
         <v>34</v>
       </c>
       <c r="K16" s="15">
-        <v>-44.117647058823</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="L16" s="15">
-        <v>-59.574468085106</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M16" s="15">
-        <v>-63.461538461538</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.949152542372</v>
+        <v>-91.286307053941</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,45 +978,45 @@
         <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>33.333333333333</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H17" s="15">
-        <v>30</v>
+        <v>54.545454545454</v>
       </c>
       <c r="I17" s="14">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="J17" s="14">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="K17" s="15">
-        <v>0</v>
+        <v>6.521739130434</v>
       </c>
       <c r="L17" s="15">
-        <v>-15.384615384615</v>
+        <v>-16.949152542372</v>
       </c>
       <c r="M17" s="15">
-        <v>37.5</v>
+        <v>44.117647058823</v>
       </c>
       <c r="N17" s="15">
-        <v>-46.341463414634</v>
+        <v>-44.943820224719</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>20</v>
@@ -1028,10 +1028,10 @@
         <v>3</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H18" s="15">
-        <v>-25</v>
+        <v>50</v>
       </c>
       <c r="I18" s="14">
         <v>17</v>
@@ -1043,13 +1043,13 @@
         <v>-22.727272727272</v>
       </c>
       <c r="L18" s="15">
-        <v>13.333333333333</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="M18" s="15">
-        <v>-37.037037037037</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.707317073170</v>
+        <v>-92.165898617511</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,60 +1057,60 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="H19" s="15">
-        <v>-31.428571428571</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="I19" s="14">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="J19" s="14">
-        <v>101</v>
+        <v>113</v>
       </c>
       <c r="K19" s="15">
-        <v>-11.881188118811</v>
+        <v>-16.814159292035</v>
       </c>
       <c r="L19" s="15">
-        <v>-24.576271186440</v>
+        <v>-26.5625</v>
       </c>
       <c r="M19" s="15">
-        <v>17.105263157894</v>
+        <v>16.049382716049</v>
       </c>
       <c r="N19" s="15">
-        <v>-59.545454545454</v>
+        <v>-59.482758620689</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>2</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
         <v>0</v>
@@ -1119,19 +1119,19 @@
         <v>11</v>
       </c>
       <c r="J20" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" s="15">
-        <v>-26.666666666666</v>
+        <v>-31.25</v>
       </c>
       <c r="L20" s="15">
         <v>10</v>
       </c>
       <c r="M20" s="15">
-        <v>175</v>
+        <v>120</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.970802919708</v>
+        <v>-92.307692307692</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="D21" s="17">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>54.545454545454</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G21" s="17">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.967741935483</v>
+        <v>-6.779661016949</v>
       </c>
       <c r="I21" s="17">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="J21" s="17">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.888888888888</v>
+        <v>-17.083333333333</v>
       </c>
       <c r="L21" s="18">
-        <v>-23.983739837398</v>
+        <v>-26.022304832713</v>
       </c>
       <c r="M21" s="18">
-        <v>-5.076142131979</v>
+        <v>-4.326923076923</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.059350503919</v>
+        <v>-78.716577540107</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G22" s="14">
         <v>1</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="14">
         <v>8</v>
       </c>
       <c r="K22" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="M22" s="15">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+        <v>4</v>
+      </c>
+      <c r="D23" s="14">
+        <v>3</v>
+      </c>
+      <c r="E23" s="15">
+        <v>33.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G23" s="14">
+        <v>9</v>
+      </c>
+      <c r="H23" s="15">
+        <v>-22.222222222222</v>
+      </c>
+      <c r="I23" s="14">
+        <v>33</v>
+      </c>
+      <c r="J23" s="14">
+        <v>41</v>
+      </c>
+      <c r="K23" s="15">
+        <v>-19.512195121951</v>
+      </c>
+      <c r="L23" s="15">
+        <v>-31.25</v>
+      </c>
+      <c r="M23" s="15">
         <v>10</v>
-      </c>
-      <c r="H23" s="15">
-        <v>-60</v>
-      </c>
-      <c r="I23" s="14">
-        <v>29</v>
-      </c>
-      <c r="J23" s="14">
-        <v>38</v>
-      </c>
-      <c r="K23" s="15">
-        <v>-23.684210526315</v>
-      </c>
-      <c r="L23" s="15">
-        <v>-38.297872340425</v>
-      </c>
-      <c r="M23" s="15">
-        <v>7.407407407407</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
+        <v>14</v>
+      </c>
+      <c r="D24" s="14">
         <v>12</v>
       </c>
-      <c r="D24" s="14">
-        <v>10</v>
-      </c>
       <c r="E24" s="15">
-        <v>20</v>
+        <v>16.666666666666</v>
       </c>
       <c r="F24" s="14">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G24" s="14">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H24" s="15">
-        <v>20</v>
+        <v>12.5</v>
       </c>
       <c r="I24" s="14">
-        <v>130</v>
+        <v>144</v>
       </c>
       <c r="J24" s="14">
-        <v>147</v>
+        <v>159</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.564625850340</v>
+        <v>-9.433962264150</v>
       </c>
       <c r="L24" s="15">
-        <v>6.557377049180</v>
+        <v>14.285714285714</v>
       </c>
       <c r="M24" s="15">
-        <v>-13.333333333333</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,13 +1303,13 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>2</v>
+      </c>
+      <c r="D25" s="14">
         <v>1</v>
       </c>
-      <c r="D25" s="14">
-        <v>3</v>
-      </c>
       <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F25" s="14">
         <v>7</v>
@@ -1321,16 +1321,16 @@
         <v>-12.5</v>
       </c>
       <c r="I25" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J25" s="14">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K25" s="15">
-        <v>-16</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="L25" s="15">
-        <v>5</v>
+        <v>9.523809523809</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>-54.545454545454</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="F26" s="14">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="G26" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H26" s="15">
-        <v>-9.523809523809</v>
+        <v>-41.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="J26" s="14">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.433734939759</v>
+        <v>-12.222222222222</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.643678160919</v>
+        <v>-15.957446808510</v>
       </c>
       <c r="M26" s="15">
-        <v>2.702702702702</v>
+        <v>-11.235955056179</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,11 +1428,11 @@
       <c r="C28" s="14">
         <v>1</v>
       </c>
-      <c r="D28" s="14">
-        <v>1</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>3</v>
@@ -1444,16 +1444,16 @@
         <v>50</v>
       </c>
       <c r="I28" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J28" s="14">
         <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>100</v>
+        <v>112.5</v>
       </c>
       <c r="L28" s="15">
-        <v>128.571428571429</v>
+        <v>112.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
+      <c r="C29" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1507,8 +1507,8 @@
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
+      <c r="C30" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1551,20 +1551,20 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F31" s="14">
+        <v>2</v>
+      </c>
+      <c r="G31" s="14">
         <v>1</v>
       </c>
-      <c r="E31" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F31" s="14">
-        <v>3</v>
-      </c>
-      <c r="G31" s="14">
-        <v>2</v>
-      </c>
       <c r="H31" s="15">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="I31" s="14">
         <v>7</v>

--- a/data/source/weekly/cs-en-us-026pct.xlsx
+++ b/data/source/weekly/cs-en-us-026pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -926,7 +926,7 @@
         <v>75</v>
       </c>
       <c r="N15" s="15">
-        <v>-12.5</v>
+        <v>-30</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
         <v>2</v>
       </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="E16" s="15">
+        <v>-50</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
         <v>4</v>
       </c>
       <c r="H16" s="15">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="I16" s="14">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J16" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="K16" s="15">
-        <v>-38.235294117647</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="L16" s="15">
-        <v>-57.142857142857</v>
+        <v>-57.692307692307</v>
       </c>
       <c r="M16" s="15">
-        <v>-61.111111111111</v>
+        <v>-62.068965517241</v>
       </c>
       <c r="N16" s="15">
-        <v>-91.286307053941</v>
+        <v>-91.472868217054</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,48 +975,48 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>-37.5</v>
       </c>
       <c r="F17" s="14">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="G17" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H17" s="15">
-        <v>54.545454545454</v>
+        <v>25</v>
       </c>
       <c r="I17" s="14">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="J17" s="14">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="K17" s="15">
-        <v>6.521739130434</v>
+        <v>-1.851851851851</v>
       </c>
       <c r="L17" s="15">
-        <v>-16.949152542372</v>
+        <v>-13.114754098360</v>
       </c>
       <c r="M17" s="15">
-        <v>44.117647058823</v>
+        <v>39.473684210526</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.943820224719</v>
+        <v>-42.391304347826</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="13" t="s">
         <v>20</v>
@@ -1025,31 +1025,31 @@
         <v>21</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H18" s="15">
-        <v>50</v>
+        <v>300</v>
       </c>
       <c r="I18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
         <v>22</v>
       </c>
       <c r="K18" s="15">
-        <v>-22.727272727272</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L18" s="15">
-        <v>-10.526315789473</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="M18" s="15">
-        <v>-39.285714285714</v>
+        <v>-37.931034482758</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.165898617511</v>
+        <v>-92.173913043478</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D19" s="14">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="E19" s="15">
-        <v>-58.333333333333</v>
+        <v>350</v>
       </c>
       <c r="F19" s="14">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G19" s="14">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="H19" s="15">
-        <v>-27.777777777777</v>
+        <v>-3.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="J19" s="14">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="K19" s="15">
-        <v>-16.814159292035</v>
+        <v>-10.434782608695</v>
       </c>
       <c r="L19" s="15">
-        <v>-26.5625</v>
+        <v>-20.155038759689</v>
       </c>
       <c r="M19" s="15">
-        <v>16.049382716049</v>
+        <v>18.390804597701</v>
       </c>
       <c r="N19" s="15">
-        <v>-59.482758620689</v>
+        <v>-56.540084388185</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>3</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>50</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
         <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="I20" s="14">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="J20" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K20" s="15">
-        <v>-31.25</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="L20" s="15">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="M20" s="15">
-        <v>120</v>
+        <v>180</v>
       </c>
       <c r="N20" s="15">
-        <v>-92.307692307692</v>
+        <v>-90.540540540540</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>-26.666666666666</v>
+        <v>35.714285714285</v>
       </c>
       <c r="F21" s="17">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="G21" s="17">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.779661016949</v>
+        <v>12.280701754386</v>
       </c>
       <c r="I21" s="17">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="J21" s="17">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="K21" s="18">
-        <v>-17.083333333333</v>
+        <v>-14.566929133858</v>
       </c>
       <c r="L21" s="18">
-        <v>-26.022304832713</v>
+        <v>-21.090909090909</v>
       </c>
       <c r="M21" s="18">
-        <v>-4.326923076923</v>
+        <v>-2.690582959641</v>
       </c>
       <c r="N21" s="18">
-        <v>-78.716577540107</v>
+        <v>-77.879714576962</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
+      <c r="C22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
+      <c r="E22" s="15">
+        <v>-100</v>
       </c>
       <c r="F22" s="14">
         <v>3</v>
       </c>
       <c r="G22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I22" s="14">
         <v>8</v>
       </c>
       <c r="J22" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L22" s="15">
         <v>60</v>
       </c>
       <c r="M22" s="15">
-        <v>60</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="F23" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H23" s="15">
-        <v>-22.222222222222</v>
+        <v>-20</v>
       </c>
       <c r="I23" s="14">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J23" s="14">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K23" s="15">
-        <v>-19.512195121951</v>
+        <v>-18.604651162790</v>
       </c>
       <c r="L23" s="15">
-        <v>-31.25</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M23" s="15">
-        <v>10</v>
+        <v>6.060606060606</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E24" s="15">
-        <v>16.666666666666</v>
+        <v>-12.5</v>
       </c>
       <c r="F24" s="14">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="G24" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="H24" s="15">
-        <v>12.5</v>
+        <v>6.818181818181</v>
       </c>
       <c r="I24" s="14">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="J24" s="14">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.433962264150</v>
+        <v>-9.580838323353</v>
       </c>
       <c r="L24" s="15">
-        <v>14.285714285714</v>
+        <v>13.533834586466</v>
       </c>
       <c r="M24" s="15">
-        <v>-11.111111111111</v>
+        <v>-12.209302325581</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14">
         <v>2</v>
       </c>
-      <c r="D25" s="14">
-        <v>1</v>
-      </c>
       <c r="E25" s="15">
-        <v>100</v>
+        <v>-50</v>
       </c>
       <c r="F25" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G25" s="14">
         <v>8</v>
       </c>
       <c r="H25" s="15">
-        <v>-12.5</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J25" s="14">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="K25" s="15">
-        <v>-11.538461538461</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L25" s="15">
-        <v>9.523809523809</v>
+        <v>9.090909090909</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>-42.857142857142</v>
+        <v>166.666666666667</v>
       </c>
       <c r="F26" s="14">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G26" s="14">
         <v>24</v>
       </c>
       <c r="H26" s="15">
-        <v>-41.666666666666</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="J26" s="14">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="K26" s="15">
-        <v>-12.222222222222</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.957446808510</v>
+        <v>-11.224489795918</v>
       </c>
       <c r="M26" s="15">
-        <v>-11.235955056179</v>
+        <v>-5.434782608695</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1426,34 +1426,34 @@
         <v>35</v>
       </c>
       <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D28" s="14">
+        <v>2</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0</v>
       </c>
       <c r="F28" s="14">
+        <v>5</v>
+      </c>
+      <c r="G28" s="14">
         <v>3</v>
       </c>
-      <c r="G28" s="14">
-        <v>2</v>
-      </c>
       <c r="H28" s="15">
-        <v>50</v>
+        <v>66.666666666666</v>
       </c>
       <c r="I28" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>112.5</v>
+        <v>90</v>
       </c>
       <c r="L28" s="15">
-        <v>112.5</v>
+        <v>137.5</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1548,8 +1548,8 @@
       <c r="A31" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>20</v>
+      <c r="C31" s="14">
+        <v>1</v>
       </c>
       <c r="D31" s="13" t="s">
         <v>20</v>
@@ -1567,16 +1567,16 @@
         <v>100</v>
       </c>
       <c r="I31" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J31" s="14">
         <v>4</v>
       </c>
       <c r="K31" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="L31" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M31" s="13" t="s">
         <v>21</v>
